--- a/backend/core/z_optimization/report_text.xlsx
+++ b/backend/core/z_optimization/report_text.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB163"/>
+  <dimension ref="A1:AB185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -23611,6 +23611,3130 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>To further boost the energy levels of this diet, consider adding energy-dense feeds like cereal grains (Maize/Corn), Rice Bran, or Molasses.</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>इस आहार की ऊर्जा और बढ़ाने के लिए अनाज (मक्का), चावल की भूसी (राइस ब्रान) या शीरा (मोलासेस) जैसी अधिक ऊर्जा वाली आहार सामग्री जोड़ने पर विचार करें।</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Para lalo pang mapataas ang enerhiya ng rasyong ito, maaaring magdagdag ng mga pakaing mataas sa enerhiya tulad ng butil (mais), darak (rice bran), o molasses.</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Untuk lebih meningkatkan energi ransum ini, pertimbangkan untuk menambahkan pakan sumber energi seperti biji-bijian (jagung), dedak padi, atau molases.</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>เพื่อเพิ่มพลังงานของสูตรอาหารนี้ให้สูงขึ้นอีก ควรพิจารณาเพิ่มอาหารที่ให้พลังงานสูง เช่น เมล็ดธัญพืช (ข้าวโพด) รำข้าว หรือกากน้ำตาล</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Để tăng thêm năng lượng cho khẩu phần này, bạn nên cân nhắc bổ sung các loại thức ăn giàu năng lượng như hạt ngũ cốc (ngô), cám gạo hoặc rỉ mật đường.</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>এই খাদ্য তালিকার শক্তি আরও বাড়াতে শক্তিসমৃদ্ধ খাদ্য, যেমন দানাশস্য (ভুট্টা), চালের কুঁড়া বা চিটাগুড় যোগ করার কথা ভাবুন।</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>यस आहारको ऊर्जा अझ बढाउन अन्न (मकै), धानको ढुटो (राइस ब्रान) वा खुदो (मोलासेस) जस्ता बढी ऊर्जा भएका दाना थप्ने विचार गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>የዚህን ራሽን የኃይል መጠን የበለጠ ለማሳደግ፣ እንደ እህል (በቆሎ)፣ የሩዝ ብራን ወይም ሞላሰስ ያሉ ከፍተኛ ኃይል ያላቸውን መኖዎች መጨመር ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Humna nyaata kanaa caalaatti dabaluuf, nyaata humna olaanaa qabu kan akka midhaanii (boqqolloo), biraanii ruuzii ykn molaasii dabaluu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>ጸዓት ናይዚ መግቢ ዝያዳ ንምውሳኽ፣ ከም እኽሊ (ዕፉን)፣ ብራን ሩዝ ወይ ሞላሰስ ዝኣመሰሉ ብጸዓት ዝሃብተሙ መግብታት ምውሳኽ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>Pour augmenter encore l'apport énergétique de cette ration, pensez à ajouter des aliments riches en énergie comme les céréales (maïs), le son de riz ou la mélasse.</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>لزيادة مستوى الطاقة في هذه العليقة، يُنصح بإضافة أعلاف غنية بالطاقة مثل الحبوب (الذرة الصفراء) أو نخالة الأرز أو المولاس (دبس السكر).</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Don ƙara kuzarin wannan abincin, ku yi la'akari da ƙara abinci mai yawan kuzari kamar hatsi (masara), dusar shinkafa, ko molasis.</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>Ili kuongeza zaidi nishati katika lishe hii, fikiria kuongeza vyakula vyenye nishati nyingi kama nafaka (mahindi), pumba za mchele au molasi.</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>Nĩguo wongerere hinya wa irio ici makĩria, ũngĩciria kũongerera irio irĩ na hinya mũingĩ ta ngano (mbembe), bran ya mũceere, kana molasses.</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>ಈ ಆಹಾರದ ಶಕ್ತಿ ಮಟ್ಟವನ್ನು ಇನ್ನಷ್ಟು ಹೆಚ್ಚಿಸಲು, ಧಾನ್ಯಗಳು (ಮೆಕ್ಕೆಜೋಳ), ಅಕ್ಕಿ ತೌಡು ಅಥವಾ ಕಾಕಂಬಿಯಂತಹ ಶಕ್ತಿ ಸಮೃದ್ಧ ಆಹಾರಗಳನ್ನು ಸೇರಿಸುವುದನ್ನು ಪರಿಗಣಿಸಿ.</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>இந்தத் தீவனத்தின் ஆற்றல் அளவை மேலும் அதிகரிக்க, தானியங்கள் (மக்காச்சோளம்), அரிசித் தவிடு அல்லது கரும்புச் சர்க்கரைப்பாகு (மொலாசஸ்) போன்ற ஆற்றல் மிகுந்த தீவனங்களைச் சேர்ப்பதைக் கருதுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>ഈ തീറ്റയിലെ ഊർജ്ജം ഇനിയും കൂട്ടാൻ, ധാന്യങ്ങൾ (ചോളം), അരിത്തവിട് അല്ലെങ്കിൽ മൊളാസസ് പോലുള്ള ഊർജ്ജസമൃദ്ധമായ തീറ്റകൾ ചേർക്കുന്നത് പരിഗണിക്കുക.</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>या आहारातील ऊर्जा आणखी वाढवण्यासाठी धान्य (मका), तांदळाचा कोंडा (राइस ब्रान) किंवा मळी (मोलॅसिस) यांसारखे जास्त ऊर्जा असलेले खाद्य घालण्याचा विचार करा.</t>
+        </is>
+      </c>
+      <c r="V164" s="2" t="inlineStr">
+        <is>
+          <t>ఈ ఆహారంలో శక్తిని ఇంకా పెంచడానికి, ధాన్యాలు (మొక్కజొన్న), వరి తవుడు లేదా మొలాసిస్ (చెరకు మడ్డి) వంటి శక్తి అధికంగా ఉండే మేతలను కలపడం పరిశీలించండి.</t>
+        </is>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>આ આહારની ઊર્જા હજુ વધારવા માટે ઊર્જાથી ભરપૂર ખોરાક, જેમ કે અનાજ (મકાઈ), ચોખાની કુશકી કે મોલાસીસ (ગોળની રસી) ઉમેરવાનું વિચારો.</t>
+        </is>
+      </c>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>इण आहार री ऊर्जा और बधावण खातर अनाज (मक्की), चावल रो चोकर (राइस ब्रान) या शीरो (मोलासेस) जिसा घणी ऊर्जा वाला दाणा मिलावण री सोचो।</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr">
+        <is>
+          <t>ଏହି ଖାଦ୍ୟର ଶକ୍ତି ଆହୁରି ବଢ଼ାଇବା ପାଇଁ ଶକ୍ତିଯୁକ୍ତ ଖାଦ୍ୟ, ଯେପରିକି ଶସ୍ୟ ଦାନା (ମକା), ଚାଉଳ କୁଣ୍ଡା କିମ୍ବା ଚିଟାଗୁଡ଼ (ମୋଲାସେସ୍) ମିଶାଇବା କଥା ବିଚାର କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z164" s="2" t="inlineStr">
+        <is>
+          <t>ਇਸ ਖੁਰਾਕ ਦੀ ਊਰਜਾ ਹੋਰ ਵਧਾਉਣ ਲਈ ਊਰਜਾ ਭਰਪੂਰ ਖੁਰਾਕੀ ਪਦਾਰਥ, ਜਿਵੇਂ ਅਨਾਜ (ਮੱਕੀ), ਚੌਲਾਂ ਦੀ ਫੱਕ (ਰਾਈਸ ਬਰੈਨ) ਜਾਂ ਸੀਰਾ ਪਾਉਣ ਬਾਰੇ ਸੋਚੋ।</t>
+        </is>
+      </c>
+      <c r="AA164" s="2" t="inlineStr">
+        <is>
+          <t>এই খাদ্যৰ শক্তি আৰু বঢ়াবলৈ শক্তিবহুল খাদ্য, যেনে শস্যৰ দানা (মাকৈ), চাউলৰ কুণ্ডা বা চিটাগুৰ (মলাছেছ) যোগ কৰাৰ কথা বিবেচনা কৰক।</t>
+        </is>
+      </c>
+      <c r="AB164" s="2" t="inlineStr">
+        <is>
+          <t>इस आहार की ऊर्जा और बधाण खातर अनाज (मक्की), चावल का चोकर (राइस ब्रान) या शीरा (मोलासेस) जिसे घणी ऊर्जा आले दाणे मिलाण की सोचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>A small addition of protein-rich feeds would help reach the optimal target for your cattle. Consider supplements like Soybean Meal or Green Legumes.</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>थोड़ी प्रोटीन-युक्त आहार सामग्री जोड़ने से आपके पशु के लिए सही लक्ष्य तक पहुँचने में मदद मिलेगी। सोयाबीन खली या हरा फलीदार चारा (जैसे बरसीम, लोबिया) जैसे पूरक देने पर विचार करें।</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Ang kaunting dagdag na pakaing mayaman sa protina ay makatutulong upang maabot ang tamang target para sa inyong mga baka. Maaaring gumamit ng supplement tulad ng soybean meal o sariwang legume.</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Sedikit tambahan pakan kaya protein akan membantu sapi Anda mencapai target optimal. Pertimbangkan pakan tambahan seperti bungkil kedelai atau leguminosa hijau.</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>การเพิ่มอาหารที่มีโปรตีนสูงอีกเล็กน้อยจะช่วยให้โคของคุณได้รับโปรตีนถึงเป้าหมายที่เหมาะสม ควรพิจารณาอาหารเสริม เช่น กากถั่วเหลือง หรือพืชตระกูลถั่วสด</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Bổ sung thêm một ít thức ăn giàu protein sẽ giúp bò của bạn đạt mức mục tiêu tối ưu. Bạn có thể dùng các loại thức ăn bổ sung như khô dầu đậu tương hoặc cây họ đậu tươi.</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>অল্প কিছু প্রোটিনসমৃদ্ধ খাদ্য যোগ করলে আপনার গবাদিপশুর জন্য সঠিক লক্ষ্যমাত্রায় পৌঁছাতে সাহায্য হবে। সয়াবিন খৈল বা সবুজ শিম্বজাতীয় ঘাসের মতো সম্পূরক খাদ্য দেওয়ার কথা ভাবুন।</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>अलिकति प्रोटिनयुक्त दाना थप्दा तपाईंको गाईभैंसीलाई उपयुक्त लक्ष्यमा पुग्न मद्दत पुग्छ। भटमासको पिना (सोयाबिन मिल) वा हरियो कोसे घाँस (जस्तै बर्सिम, स्टाइलो) जस्ता पूरक दिने विचार गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>በፕሮቲን የበለጸጉ መኖዎችን በጥቂቱ መጨመር ከብቶችዎ ተገቢውን ግብ እንዲያሟሉ ይረዳል። እንደ የአኩሪ አተር ፋጉሎ ወይም አረንጓዴ የጥራጥሬ መኖ (ለምሳሌ አልፋልፋ) ያሉ ተጨማሪዎችን ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Nyaata pirootiiniin badhaadhe xiqqoo dabaluun horiin keessan galma sirrii akka ga'u ni gargaara. Dabalata akka faagulloo soyaabiinii ykn nyaata gosa ataraa magariisaa (fkn. alfaalfaa) yaadaa.</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>ብፕሮቲን ዝሃብተሙ መግብታት ቁሩብ ምውሳኽ ከብትኹም ቅኑዕ ዕላማ ክበጽሑ ክሕግዝ እዩ። ከም ፋጉሎ ሶያ ወይ ቀጠልያ ጥረ-ኣእካል መግቢ (ንኣብነት ኣልፋልፋ) ዝኣመሰሉ ተወሰኽቲ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>Un petit ajout d'aliments riches en protéines aiderait à atteindre l'objectif optimal pour vos bovins. Pensez à des compléments comme le tourteau de soja ou les légumineuses vertes.</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>إضافة كمية صغيرة من الأعلاف الغنية بالبروتين ستساعد على بلوغ الهدف الأمثل لماشيتك. يُنصح بمكمّلات مثل كسب فول الصويا أو البقوليات الخضراء.</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Ƙara ɗan abinci mai yawan furotin zai taimaka wa shanunku su kai ga matakin da ya dace. Ku yi la'akari da ƙarin abinci kamar kantun waken soya ko ɗanyen harawa (kamar ta wake ko gyaɗa).</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>Kuongeza kidogo vyakula vyenye protini nyingi kutasaidia ng'ombe wako kufikia lengo bora. Fikiria virutubisho kama mashudu ya soya au mikunde ya kijani.</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>Kũongerera hanini irio irĩ na protein nyingĩ nĩ gũgũteithia ng'ombe ciaku gũkinya kĩrĩa kĩbataranĩtie. Ciria irio cia kũongerera ta soya meal kana mĩmera nduru ya mũthemba wa mboco (ta desmodium kana lucerne).</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>ಸ್ವಲ್ಪ ಪ್ರೋಟೀನ್ ಸಮೃದ್ಧ ಆಹಾರವನ್ನು ಸೇರಿಸಿದರೆ ನಿಮ್ಮ ಜಾನುವಾರುಗಳಿಗೆ ಸೂಕ್ತ ಗುರಿ ತಲುಪಲು ಸಹಾಯವಾಗುತ್ತದೆ. ಸೋಯಾಬೀನ್ ಹಿಂಡಿ ಅಥವಾ ಹಸಿರು ದ್ವಿದಳ ಮೇವಿನಂತಹ ಪೂರಕಗಳನ್ನು ಪರಿಗಣಿಸಿ.</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>புரதச்சத்து மிகுந்த தீவனங்களைச் சிறிது சேர்த்தால் உங்கள் கால்நடைகள் உகந்த இலக்கை அடைய உதவும். சோயாபீன் புண்ணாக்கு அல்லது பயறுவகைப் பசுந்தீவனம் போன்ற துணைத் தீவனங்களைக் கருதுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>പ്രോട്ടീൻ സമൃദ്ധമായ തീറ്റകൾ അല്പം ചേർത്താൽ നിങ്ങളുടെ കന്നുകാലികൾക്ക് ഉചിതമായ ലക്ഷ്യത്തിലെത്താൻ സഹായകമാകും. സോയാബീൻ പിണ്ണാക്ക് അല്ലെങ്കിൽ പയർവർഗ്ഗ പച്ചത്തീറ്റ പോലുള്ള അനുബന്ധ തീറ്റകൾ പരിഗണിക്കുക.</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>थोडे प्रथिनयुक्त खाद्य घातल्यास तुमच्या जनावरांसाठी योग्य लक्ष्य गाठण्यास मदत होईल. सोयाबीन पेंड किंवा हिरवा द्विदल चारा (उदा. लसूणघास, बरसीम) यांसारखे पूरक खाद्य देण्याचा विचार करा.</t>
+        </is>
+      </c>
+      <c r="V165" s="2" t="inlineStr">
+        <is>
+          <t>ప్రోటీన్ అధికంగా ఉండే మేతను కొంచెం కలిపితే మీ పశువులు సరైన లక్ష్యాన్ని చేరుకోవడానికి సహాయపడుతుంది. సోయాబీన్ చెక్క లేదా పప్పుజాతి పచ్చి గ్రాసం వంటి అనుబంధ మేతలను పరిశీలించండి.</t>
+        </is>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>થોડો પ્રોટીનથી ભરપૂર ખોરાક ઉમેરવાથી તમારા પશુઓ માટે યોગ્ય લક્ષ્ય સુધી પહોંચવામાં મદદ મળશે. સોયાબીન ખોળ કે લીલો કઠોળવર્ગીય ચારો (જેમ કે રજકો) જેવા પૂરક આપવાનું વિચારો.</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>थोड़ो प्रोटीन वालो दाणो मिलावण सूं थारा पशुआं नै सही लक्ष्य तांई पूगण में मदद मिलैला। सोयाबीन री खल या हरो फलीदार चारो (जियां रिजको, बरसीम) जिसा पूरक देवण री सोचो।</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr">
+        <is>
+          <t>ଅଳ୍ପ ପ୍ରୋଟିନଯୁକ୍ତ ଖାଦ୍ୟ ମିଶାଇଲେ ଆପଣଙ୍କ ଗାଈଗୋରୁଙ୍କ ପାଇଁ ଉପଯୁକ୍ତ ଲକ୍ଷ୍ୟରେ ପହଞ୍ଚିବାରେ ସାହାଯ୍ୟ ହେବ। ସୋୟାବିନ୍ ପିଡ଼ିଆ କିମ୍ବା ସବୁଜ ଡାଲିଜାତୀୟ ଚାରା ଭଳି ପରିପୂରକ ଖାଦ୍ୟ ଦେବା କଥା ବିଚାର କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z165" s="2" t="inlineStr">
+        <is>
+          <t>ਥੋੜ੍ਹੇ ਜਿਹੇ ਪ੍ਰੋਟੀਨ ਭਰਪੂਰ ਖੁਰਾਕੀ ਪਦਾਰਥ ਪਾਉਣ ਨਾਲ ਤੁਹਾਡੇ ਪਸ਼ੂਆਂ ਲਈ ਸਹੀ ਟੀਚਾ ਹਾਸਲ ਕਰਨ ਵਿੱਚ ਮਦਦ ਮਿਲੇਗੀ। ਸੋਇਆਬੀਨ ਦੀ ਖਲ ਜਾਂ ਹਰੇ ਫਲੀਦਾਰ ਚਾਰੇ (ਜਿਵੇਂ ਬਰਸੀਮ) ਵਰਗੇ ਪੂਰਕ ਦੇਣ ਬਾਰੇ ਸੋਚੋ।</t>
+        </is>
+      </c>
+      <c r="AA165" s="2" t="inlineStr">
+        <is>
+          <t>অলপ প্ৰ'টিনযুক্ত খাদ্য যোগ কৰিলে আপোনাৰ গৰুৰ বাবে উপযুক্ত লক্ষ্যত উপনীত হোৱাত সহায় হ'ব। ছয়াবিনৰ খইল বা সেউজীয়া মাহজাতীয় ঘাঁহৰ দৰে পৰিপূৰক খাদ্য দিয়াৰ কথা বিবেচনা কৰক।</t>
+        </is>
+      </c>
+      <c r="AB165" s="2" t="inlineStr">
+        <is>
+          <t>थोड़ा प्रोटीन आला दाणा मिलाण तै थारे पशुआं नै सही लक्ष्य ताईं पहोंचण म्ह मदद मिलैगी। सोयाबीन की खल या हरा फलीदार चारा (जिसे बरसीम, लोबिया) जिसे पूरक देण की सोचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>This diet would benefit from additional energy sources. Try including more grains or high-energy concentrates to meet the ideal target.</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>इस आहार में अतिरिक्त ऊर्जा स्रोतों से लाभ होगा। आदर्श लक्ष्य तक पहुँचने के लिए अधिक अनाज या अधिक ऊर्जा वाला दाना शामिल करके देखें।</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Makabubuti sa rasyong ito ang dagdag na pinagmumulan ng enerhiya. Subukang magdagdag ng mas maraming butil o high-energy na concentrate upang maabot ang tamang target.</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Ransum ini akan lebih baik dengan tambahan sumber energi. Cobalah menambah biji-bijian atau konsentrat berenergi tinggi untuk mencapai target ideal.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>สูตรอาหารนี้ควรได้รับแหล่งพลังงานเพิ่มเติม ลองเพิ่มเมล็ดธัญพืชหรืออาหารข้นพลังงานสูงให้มากขึ้น เพื่อให้ถึงเป้าหมายที่เหมาะสม</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Khẩu phần này nên được bổ sung thêm nguồn năng lượng. Hãy thử thêm hạt ngũ cốc hoặc thức ăn tinh giàu năng lượng để đạt mục tiêu lý tưởng.</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>এই খাদ্য তালিকায় আরও শক্তির উৎস যোগ করলে ভালো হবে। আদর্শ লক্ষ্যমাত্রায় পৌঁছাতে আরও দানাশস্য বা উচ্চ-শক্তির দানাদার খাদ্য যোগ করে দেখুন।</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>यस आहारमा थप ऊर्जाका स्रोत राख्दा फाइदा हुन्छ। आदर्श लक्ष्यमा पुग्न बढी अन्न वा बढी ऊर्जा भएको दाना समावेश गरेर हेर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>ይህ ራሽን ተጨማሪ የኃይል ምንጮች ቢጨመሩለት ይሻሻላል። ተገቢውን ግብ ለማሟላት ተጨማሪ እህል ወይም ከፍተኛ ኃይል ያላቸውን ኮንሰንትሬቶች ለማካተት ይሞክሩ።</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Nyaanni kun madda humnaa dabalataatiin ni fooyya'a. Galma sirrii ga'uuf midhaan dabalataa ykn nyaata dabalataa humna olaanaa qabu itti dabaluu yaalaa.</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>እዚ መግቢ ተወሳኺ ምንጪ ጸዓት እንተ ተወሲኽዎ ይመሓየሽ። ቅኑዕ ዕላማ ንምብጻሕ ተወሳኺ እኽሊ ወይ ብጸዓት ዝሃብተሙ ኮንሰንትሬት ንምእታው ፈትኑ።</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>Cette ration gagnerait à recevoir des sources d'énergie supplémentaires. Essayez d'ajouter plus de céréales ou de concentrés riches en énergie pour atteindre l'objectif idéal.</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>ستستفيد هذه العليقة من مصادر طاقة إضافية. حاول إدخال مزيد من الحبوب أو المركزات عالية الطاقة لبلوغ الهدف المثالي.</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Wannan abincin zai amfana da ƙarin hanyoyin kuzari. Ku gwada ƙara hatsi ko abincin ƙari mai yawan kuzari don cimma matakin da ya dace.</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>Lishe hii itafaidika na vyanzo vya ziada vya nishati. Jaribu kuongeza nafaka zaidi au chakula cha nyongeza chenye nishati nyingi ili kufikia lengo bora.</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>Irio ici no ciagĩrĩre makĩria ingĩongererwo hinya. Geria kũongerera ngano makĩria kana irio cia kũongerera irĩ na hinya mũingĩ nĩguo ũkinyie kĩrĩa kĩbataranĩtie.</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>ಈ ಆಹಾರಕ್ಕೆ ಹೆಚ್ಚುವರಿ ಶಕ್ತಿ ಮೂಲಗಳು ಪ್ರಯೋಜನಕಾರಿ. ಆದರ್ಶ ಗುರಿ ತಲುಪಲು ಹೆಚ್ಚು ಧಾನ್ಯಗಳನ್ನು ಅಥವಾ ಹೆಚ್ಚು ಶಕ್ತಿಯುಳ್ಳ ಸಾಂದ್ರ ಆಹಾರವನ್ನು ಸೇರಿಸಿ ನೋಡಿ.</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>இந்தத் தீவனத்திற்குக் கூடுதல் ஆற்றல் ஆதாரங்கள் பயனளிக்கும். சிறந்த இலக்கை அடைய அதிக தானியங்கள் அல்லது ஆற்றல் மிகுந்த அடர் தீவனங்களைச் சேர்த்துப் பாருங்கள்.</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>ഈ തീറ്റയ്ക്ക് കൂടുതൽ ഊർജ്ജ സ്രോതസ്സുകൾ ഗുണം ചെയ്യും. അനുയോജ്യമായ ലക്ഷ്യത്തിലെത്താൻ കൂടുതൽ ധാന്യങ്ങളോ ഉയർന്ന ഊർജ്ജമുള്ള സാന്ദ്രീകൃതാഹാരങ്ങളോ ചേർത്തു നോക്കുക.</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>या आहारात अधिक ऊर्जा स्रोत जोडल्यास फायदा होईल. आदर्श लक्ष्य गाठण्यासाठी अधिक धान्य किंवा जास्त ऊर्जेचे पशुखाद्य समाविष्ट करून पाहा.</t>
+        </is>
+      </c>
+      <c r="V166" s="2" t="inlineStr">
+        <is>
+          <t>ఈ ఆహారానికి అదనపు శక్తి వనరులు మేలు చేస్తాయి. సరైన లక్ష్యాన్ని చేరుకోవడానికి మరిన్ని ధాన్యాలు లేదా అధిక శక్తి గల దాణాను కలిపి చూడండి.</t>
+        </is>
+      </c>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>આ આહારમાં ઊર્જાના વધારાના સ્ત્રોત ઉમેરવાથી ફાયદો થશે. આદર્શ લક્ષ્ય સુધી પહોંચવા માટે વધુ અનાજ કે વધુ ઊર્જાવાળું દાણ ઉમેરી જુઓ.</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>इण आहार में और ऊर्जा रा स्रोत मिलावण सूं फायदो होवैला। आदर्श लक्ष्य तांई पूगण खातर बेसी अनाज या घणी ऊर्जा वालो दाणो मिलाय नै देखो।</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr">
+        <is>
+          <t>ଏହି ଖାଦ୍ୟରେ ଅଧିକ ଶକ୍ତି ଉତ୍ସ ମିଶାଇଲେ ଭଲ ହେବ। ଆଦର୍ଶ ଲକ୍ଷ୍ୟରେ ପହଞ୍ଚିବା ପାଇଁ ଅଧିକ ଶସ୍ୟ ଦାନା କିମ୍ବା ଉଚ୍ଚ ଶକ୍ତିଯୁକ୍ତ ଦାନାଦାର ଖାଦ୍ୟ ମିଶାଇ ଦେଖନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z166" s="2" t="inlineStr">
+        <is>
+          <t>ਇਸ ਖੁਰਾਕ ਵਿੱਚ ਊਰਜਾ ਦੇ ਹੋਰ ਸਰੋਤ ਪਾਉਣ ਨਾਲ ਫ਼ਾਇਦਾ ਹੋਵੇਗਾ। ਆਦਰਸ਼ ਟੀਚੇ ਤੱਕ ਪਹੁੰਚਣ ਲਈ ਵੱਧ ਅਨਾਜ ਜਾਂ ਵੱਧ ਊਰਜਾ ਵਾਲਾ ਦਾਣਾ ਪਾ ਕੇ ਦੇਖੋ।</t>
+        </is>
+      </c>
+      <c r="AA166" s="2" t="inlineStr">
+        <is>
+          <t>এই খাদ্যত অতিৰিক্ত শক্তিৰ উৎস যোগ কৰিলে ভাল হ'ব। আদৰ্শ লক্ষ্যত উপনীত হ'বলৈ অধিক শস্যৰ দানা বা উচ্চ শক্তিৰ দানাদাৰ খাদ্য অন্তৰ্ভুক্ত কৰি চাওক।</t>
+        </is>
+      </c>
+      <c r="AB166" s="2" t="inlineStr">
+        <is>
+          <t>इस आहार म्ह और ऊर्जा के स्रोत मिलाण तै फायदा होगा। आदर्श लक्ष्य ताईं पहोंचण खातर और घणा अनाज या घणी ऊर्जा आला दाणा मिला कै देखो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>To reach the ideal protein balance, consider increasing protein-rich feed sources in your selection.</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>आदर्श प्रोटीन संतुलन तक पहुँचने के लिए अपनी चुनी हुई आहार सामग्री में प्रोटीन-युक्त स्रोत बढ़ाने पर विचार करें।</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Para maabot ang tamang balanse ng protina, maaaring dagdagan ang mga pakaing mayaman sa protina sa inyong pinili.</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Untuk mencapai keseimbangan protein yang ideal, pertimbangkan untuk menambah sumber pakan kaya protein dalam pilihan Anda.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>เพื่อให้ได้สมดุลโปรตีนที่เหมาะสม ควรพิจารณาเพิ่มแหล่งอาหารที่มีโปรตีนสูงในรายการอาหารที่คุณเลือก</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Để đạt cân bằng protein lý tưởng, bạn nên cân nhắc tăng các nguồn thức ăn giàu protein trong danh sách đã chọn.</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>প্রোটিনের আদর্শ ভারসাম্যে পৌঁছাতে আপনার নির্বাচনে প্রোটিনসমৃদ্ধ খাদ্যের পরিমাণ বাড়ানোর কথা ভাবুন।</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>प्रोटिनको आदर्श सन्तुलनमा पुग्न तपाईंले छानेका दाना-घाँसमा प्रोटिनयुक्त स्रोत बढाउने विचार गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>ተገቢውን የፕሮቲን ሚዛን ለማግኘት፣ በመረጧቸው መኖዎች ውስጥ በፕሮቲን የበለጸጉ መኖዎችን መጨመር ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Madaallii pirootiinii sirrii ga'uuf, nyaata filattan keessatti madda nyaataa pirootiiniin badhaadhe dabaluu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>ቅኑዕ ሚዛን ፕሮቲን ንምብጻሕ፣ ኣብ ዝመረጽኩምዎ መግብታት ብፕሮቲን ዝሃብተሙ ምንጭታት ምውሳኽ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>Pour atteindre l'équilibre protéique idéal, pensez à augmenter la part d'aliments riches en protéines dans votre sélection.</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>لبلوغ التوازن المثالي للبروتين، يُنصح بزيادة مصادر الأعلاف الغنية بالبروتين في اختيارك.</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Don samun daidaiton furotin da ya dace, ku yi la'akari da ƙara abinci mai yawan furotin cikin zaɓinku.</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>Ili kufikia mizani bora ya protini, fikiria kuongeza vyanzo vya chakula vyenye protini nyingi katika uchaguzi wako.</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>Nĩguo ũkinyie mũiganĩro mwega wa protein, ciria kũongerera irio irĩ na protein nyingĩ harĩ iria ũthuurĩte.</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>ಆದರ್ಶ ಪ್ರೋಟೀನ್ ಸಮತೋಲನ ತಲುಪಲು, ನಿಮ್ಮ ಆಯ್ಕೆಯಲ್ಲಿ ಪ್ರೋಟೀನ್ ಸಮೃದ್ಧ ಆಹಾರ ಮೂಲಗಳನ್ನು ಹೆಚ್ಚಿಸುವುದನ್ನು ಪರಿಗಣಿಸಿ.</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>சிறந்த புரதச் சமநிலையை அடைய, உங்கள் தேர்வில் புரதச்சத்து மிகுந்த தீவனங்களை அதிகரிப்பதைக் கருதுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>അനുയോജ്യമായ പ്രോട്ടീൻ സന്തുലനത്തിലെത്താൻ, നിങ്ങളുടെ തിരഞ്ഞെടുപ്പിൽ പ്രോട്ടീൻ സമൃദ്ധമായ തീറ്റകൾ കൂട്ടുന്നത് പരിഗണിക്കുക.</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>प्रथिनांचे आदर्श संतुलन गाठण्यासाठी तुमच्या निवडीतील प्रथिनयुक्त खाद्याचे स्रोत वाढवण्याचा विचार करा.</t>
+        </is>
+      </c>
+      <c r="V167" s="2" t="inlineStr">
+        <is>
+          <t>సరైన ప్రోటీన్ సమతుల్యత కోసం, మీ ఎంపికలో ప్రోటీన్ అధికంగా ఉండే మేతలను పెంచడం పరిశీలించండి.</t>
+        </is>
+      </c>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>પ્રોટીનનું આદર્શ સંતુલન મેળવવા માટે તમારી પસંદગીમાં પ્રોટીનથી ભરપૂર ખોરાક વધારવાનું વિચારો.</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>प्रोटीन रो आदर्श संतुलन पावण खातर थारा चुण्योड़ा दाणा-चारा में प्रोटीन वाला स्रोत बधावण री सोचो।</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr">
+        <is>
+          <t>ପ୍ରୋଟିନର ଆଦର୍ଶ ସନ୍ତୁଳନରେ ପହଞ୍ଚିବା ପାଇଁ ଆପଣଙ୍କ ଚୟନରେ ପ୍ରୋଟିନଯୁକ୍ତ ଖାଦ୍ୟର ପରିମାଣ ବଢ଼ାଇବା କଥା ବିଚାର କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z167" s="2" t="inlineStr">
+        <is>
+          <t>ਪ੍ਰੋਟੀਨ ਦਾ ਆਦਰਸ਼ ਸੰਤੁਲਨ ਹਾਸਲ ਕਰਨ ਲਈ ਆਪਣੀ ਚੋਣ ਵਿੱਚ ਪ੍ਰੋਟੀਨ ਭਰਪੂਰ ਖੁਰਾਕੀ ਪਦਾਰਥ ਵਧਾਉਣ ਬਾਰੇ ਸੋਚੋ।</t>
+        </is>
+      </c>
+      <c r="AA167" s="2" t="inlineStr">
+        <is>
+          <t>প্ৰ'টিনৰ আদৰ্শ ভাৰসাম্যত উপনীত হ'বলৈ আপোনাৰ বাছনিত প্ৰ'টিনযুক্ত খাদ্যৰ পৰিমাণ বঢ়োৱাৰ কথা বিবেচনা কৰক।</t>
+        </is>
+      </c>
+      <c r="AB167" s="2" t="inlineStr">
+        <is>
+          <t>प्रोटीन का आदर्श संतुलन पाण खातर अपणे चुणे होए दाणे-चारे म्ह प्रोटीन आले स्रोत बधाण की सोचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Calcium levels are slightly below the ideal target. Consider adding a mineral supplement or calcium-rich feeds to reach the goal.</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>कैल्शियम का स्तर आदर्श लक्ष्य से थोड़ा कम है। लक्ष्य तक पहुँचने के लिए खनिज पूरक या कैल्शियम-युक्त आहार सामग्री जोड़ने पर विचार करें।</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Bahagyang mababa ang calcium kaysa sa tamang target. Maaaring magdagdag ng mineral supplement o mga pakaing mayaman sa calcium upang maabot ito.</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Kadar kalsium sedikit di bawah target ideal. Pertimbangkan untuk menambahkan suplemen mineral atau pakan kaya kalsium agar target tercapai.</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>ระดับแคลเซียมต่ำกว่าเป้าหมายที่เหมาะสมเล็กน้อย ควรพิจารณาเพิ่มแร่ธาตุเสริมหรืออาหารที่มีแคลเซียมสูงเพื่อให้ถึงเป้าหมาย</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Hàm lượng canxi hơi thấp hơn mục tiêu lý tưởng. Bạn nên cân nhắc bổ sung khoáng hoặc thức ăn giàu canxi để đạt mục tiêu.</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>ক্যালসিয়ামের মাত্রা আদর্শ লক্ষ্যমাত্রার চেয়ে সামান্য কম। লক্ষ্যে পৌঁছাতে খনিজ সম্পূরক বা ক্যালসিয়ামসমৃদ্ধ খাদ্য যোগ করার কথা ভাবুন।</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>क्याल्सियमको मात्रा आदर्श लक्ष्यभन्दा अलि कम छ। लक्ष्यमा पुग्न खनिज पूरक वा क्याल्सियमयुक्त दाना थप्ने विचार गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>የካልሲየም መጠን ከተገቢው ግብ በትንሹ ያነሰ ነው። ግቡን ለማሟላት የማዕድን ተጨማሪ ወይም በካልሲየም የበለጸጉ መኖዎችን መጨመር ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Hammi kaalsiyeemii galma sirrii irraa xiqqoo gadi. Galma ga'uuf dabalata albuudaa ykn nyaata kaalsiyeemiin badhaadhe dabaluu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>መጠን ካልሲየም ካብ ቅኑዕ ዕላማ ቁሩብ ትሑት እዩ። ዕላማ ንምብጻሕ ተወሳኺ ማዕድን ወይ ብካልሲየም ዝሃብተሙ መግብታት ምውሳኽ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>Le niveau de calcium est légèrement inférieur à l'objectif idéal. Pensez à ajouter un complément minéral ou des aliments riches en calcium pour l'atteindre.</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>مستوى الكالسيوم أقل قليلًا من الهدف المثالي. يُنصح بإضافة مكمّل معدني أو أعلاف غنية بالكالسيوم لبلوغ الهدف.</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Yawan kalsiyam ya ɗan gaza matakin da ya dace. Ku yi la'akari da ƙara ma'adinai ko abinci mai yawan kalsiyam don cimma burin.</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>Kiwango cha kalsiamu kiko chini kidogo ya lengo bora. Fikiria kuongeza kirutubisho cha madini au vyakula vyenye kalsiamu nyingi ili kufikia lengo.</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>Calcium nĩ nini hanini gũkĩra kĩrĩa kĩbataranĩtie. Ciria kũongerera mineral kana irio irĩ na calcium nyingĩ nĩguo ũkinyie muoroto.</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>ಕ್ಯಾಲ್ಸಿಯಂ ಮಟ್ಟ ಆದರ್ಶ ಗುರಿಗಿಂತ ಸ್ವಲ್ಪ ಕಡಿಮೆ ಇದೆ. ಗುರಿ ತಲುಪಲು ಖನಿಜ ಪೂರಕ ಅಥವಾ ಕ್ಯಾಲ್ಸಿಯಂ ಸಮೃದ್ಧ ಆಹಾರಗಳನ್ನು ಸೇರಿಸುವುದನ್ನು ಪರಿಗಣಿಸಿ.</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>கால்சியம் அளவு சிறந்த இலக்கை விடச் சற்றுக் குறைவாக உள்ளது. இலக்கை அடைய தாது உப்புத் துணைத் தீவனம் அல்லது கால்சியம் மிகுந்த தீவனங்களைச் சேர்ப்பதைக் கருதுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>കാൽസ്യത്തിന്റെ അളവ് അനുയോജ്യമായ ലക്ഷ്യത്തേക്കാൾ അല്പം കുറവാണ്. ലക്ഷ്യത്തിലെത്താൻ ധാതുലവണ അനുബന്ധമോ കാൽസ്യം സമൃദ്ധമായ തീറ്റകളോ ചേർക്കുന്നത് പരിഗണിക്കുക.</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>कॅल्शियमचे प्रमाण आदर्श लक्ष्यापेक्षा थोडे कमी आहे. लक्ष्य गाठण्यासाठी खनिज पूरक किंवा कॅल्शियमयुक्त खाद्य घालण्याचा विचार करा.</t>
+        </is>
+      </c>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>కాల్షియం స్థాయి సరైన లక్ష్యం కంటే కొంచెం తక్కువగా ఉంది. లక్ష్యాన్ని చేరుకోవడానికి ఖనిజ లవణ అనుబంధం లేదా కాల్షియం అధికంగా ఉండే మేతలను కలపడం పరిశీలించండి.</t>
+        </is>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>કેલ્શિયમનું પ્રમાણ આદર્શ લક્ષ્ય કરતાં થોડું ઓછું છે. લક્ષ્ય સુધી પહોંચવા માટે ખનીજ પૂરક કે કેલ્શિયમથી ભરપૂર ખોરાક ઉમેરવાનું વિચારો.</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>कैल्शियम री मात्रा आदर्श लक्ष्य सूं थोड़ी कम है। लक्ष्य तांई पूगण खातर खनिज पूरक या कैल्शियम वालो दाणो मिलावण री सोचो।</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr">
+        <is>
+          <t>କ୍ୟାଲସିୟମ ମାତ୍ରା ଆଦର୍ଶ ଲକ୍ଷ୍ୟଠାରୁ ସାମାନ୍ୟ କମ୍। ଲକ୍ଷ୍ୟରେ ପହଞ୍ଚିବା ପାଇଁ ଖଣିଜ ପରିପୂରକ କିମ୍ବା କ୍ୟାଲସିୟମଯୁକ୍ତ ଖାଦ୍ୟ ମିଶାଇବା କଥା ବିଚାର କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z168" s="2" t="inlineStr">
+        <is>
+          <t>ਕੈਲਸ਼ੀਅਮ ਦੀ ਮਾਤਰਾ ਆਦਰਸ਼ ਟੀਚੇ ਤੋਂ ਥੋੜ੍ਹੀ ਘੱਟ ਹੈ। ਟੀਚੇ ਤੱਕ ਪਹੁੰਚਣ ਲਈ ਖਣਿਜ ਪੂਰਕ ਜਾਂ ਕੈਲਸ਼ੀਅਮ ਭਰਪੂਰ ਖੁਰਾਕੀ ਪਦਾਰਥ ਪਾਉਣ ਬਾਰੇ ਸੋਚੋ।</t>
+        </is>
+      </c>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>কেলচিয়ামৰ মাত্ৰা আদৰ্শ লক্ষ্যতকৈ অলপ কম। লক্ষ্যত উপনীত হ'বলৈ খনিজ পৰিপূৰক বা কেলচিয়ামযুক্ত খাদ্য যোগ কৰাৰ কথা বিবেচনা কৰক।</t>
+        </is>
+      </c>
+      <c r="AB168" s="2" t="inlineStr">
+        <is>
+          <t>कैल्शियम की मात्रा आदर्श लक्ष्य तै थोड़ी कम सै। लक्ष्य ताईं पहोंचण खातर खनिज पूरक या कैल्शियम आला दाणा मिलाण की सोचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Phosphorus levels could be improved to reach the target. Consider adding a mineral mix or rice bran.</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>लक्ष्य तक पहुँचने के लिए फॉस्फोरस का स्तर सुधारा जा सकता है। खनिज मिश्रण या चावल की भूसी (राइस ब्रान) जोड़ने पर विचार करें।</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Maaari pang mapabuti ang phosphorus upang maabot ang target. Maaaring magdagdag ng mineral mix o darak (rice bran).</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Kadar fosfor masih dapat ditingkatkan untuk mencapai target. Pertimbangkan untuk menambahkan mineral campuran atau dedak padi.</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>ระดับฟอสฟอรัสยังปรับปรุงให้ถึงเป้าหมายได้ ควรพิจารณาเพิ่มแร่ธาตุผสมหรือรำข้าว</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Hàm lượng phốt pho có thể được cải thiện để đạt mục tiêu. Bạn nên cân nhắc bổ sung khoáng hỗn hợp hoặc cám gạo.</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>লক্ষ্যমাত্রায় পৌঁছাতে ফসফরাসের মাত্রা আরও উন্নত করা যেতে পারে। খনিজ মিশ্রণ বা চালের কুঁড়া যোগ করার কথা ভাবুন।</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>लक्ष्यमा पुग्न फस्फोरसको मात्रा सुधार गर्न सकिन्छ। खनिज मिश्रण वा धानको ढुटो थप्ने विचार गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>ግቡን ለማሟላት የፎስፈረስ መጠን ሊሻሻል ይችላል። የማዕድን ድብልቅ ወይም የሩዝ ብራን መጨመር ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Galma ga'uuf hammi fosfarasii fooyya'uu danda'a. Makaa albuudaa ykn biraanii ruuzii dabaluu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>ዕላማ ንምብጻሕ መጠን ፎስፎረስ ክመሓየሽ ይኽእል እዩ። ሕዋስ ማዕድን ወይ ብራን ሩዝ ምውሳኽ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>Le niveau de phosphore pourrait être amélioré pour atteindre l'objectif. Pensez à ajouter un mélange minéral ou du son de riz.</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>يمكن تحسين مستوى الفوسفور لبلوغ الهدف. يُنصح بإضافة خليط معدني أو نخالة الأرز.</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Ana iya inganta yawan fosfores don cimma burin. Ku yi la'akari da ƙara gaurayen ma'adinai ko dusar shinkafa.</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>Kiwango cha fosforasi kinaweza kuboreshwa ili kufikia lengo. Fikiria kuongeza mchanganyiko wa madini au pumba za mchele.</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>Phosphorus no yongererwo nĩguo ĩkinyie muoroto. Ciria kũongerera mineral mix kana bran ya mũceere.</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>ಗುರಿ ತಲುಪಲು ರಂಜಕದ ಮಟ್ಟವನ್ನು ಸುಧಾರಿಸಬಹುದು. ಖನಿಜ ಮಿಶ್ರಣ ಅಥವಾ ಅಕ್ಕಿ ತೌಡು ಸೇರಿಸುವುದನ್ನು ಪರಿಗಣಿಸಿ.</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>இலக்கை அடைய பாஸ்பரஸ் அளவை மேம்படுத்தலாம். தாது உப்புக் கலவை அல்லது அரிசித் தவிடு சேர்ப்பதைக் கருதுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>ലക്ഷ്യത്തിലെത്താൻ ഫോസ്ഫറസിന്റെ അളവ് മെച്ചപ്പെടുത്താവുന്നതാണ്. ധാതുലവണ മിശ്രിതമോ അരിത്തവിടോ ചേർക്കുന്നത് പരിഗണിക്കുക.</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>लक्ष्य गाठण्यासाठी फॉस्फरसचे प्रमाण सुधारता येईल. खनिज मिश्रण किंवा तांदळाचा कोंडा घालण्याचा विचार करा.</t>
+        </is>
+      </c>
+      <c r="V169" s="2" t="inlineStr">
+        <is>
+          <t>లక్ష్యాన్ని చేరుకోవడానికి భాస్వరం స్థాయిని మెరుగుపరచవచ్చు. ఖనిజ లవణ మిశ్రమం లేదా వరి తవుడు కలపడం పరిశీలించండి.</t>
+        </is>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>લક્ષ્ય સુધી પહોંચવા માટે ફોસ્ફરસનું પ્રમાણ સુધારી શકાય છે. ખનીજ મિશ્રણ કે ચોખાની કુશકી ઉમેરવાનું વિચારો.</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>फॉस्फोरस री मात्रा लक्ष्य तांई पूगावण खातर सुधारी जा सकै। खनिज मिश्रण या चावल रो चोकर मिलावण री सोचो।</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr">
+        <is>
+          <t>ଲକ୍ଷ୍ୟରେ ପହଞ୍ଚିବା ପାଇଁ ଫସଫରସ ମାତ୍ରା ଉନ୍ନତ କରାଯାଇପାରେ। ଖଣିଜ ମିଶ୍ରଣ କିମ୍ବା ଚାଉଳ କୁଣ୍ଡା ମିଶାଇବା କଥା ବିଚାର କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z169" s="2" t="inlineStr">
+        <is>
+          <t>ਟੀਚੇ ਤੱਕ ਪਹੁੰਚਣ ਲਈ ਫ਼ਾਸਫ਼ੋਰਸ ਦੀ ਮਾਤਰਾ ਸੁਧਾਰੀ ਜਾ ਸਕਦੀ ਹੈ। ਧਾਤਾਂ ਦਾ ਚੂਰਾ (ਮਿਨਰਲ ਮਿਕਸਚਰ) ਜਾਂ ਚੌਲਾਂ ਦੀ ਫੱਕ ਪਾਉਣ ਬਾਰੇ ਸੋਚੋ।</t>
+        </is>
+      </c>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>লক্ষ্যত উপনীত হ'বলৈ ফছফৰাছৰ মাত্ৰা উন্নত কৰিব পাৰি। খনিজ মিশ্ৰণ বা চাউলৰ কুণ্ডা যোগ কৰাৰ কথা বিবেচনা কৰক।</t>
+        </is>
+      </c>
+      <c r="AB169" s="2" t="inlineStr">
+        <is>
+          <t>फॉस्फोरस की मात्रा लक्ष्य ताईं पहोंचाण खातर सुधारी जा सकै सै। खनिज मिश्रण या चावल का चोकर मिलाण की सोचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Adding a bit more dry fodder (Straw/Stover) or high-quality grasses would support better rumen health and fiber balance.</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>थोड़ा और सूखा चारा (भूसा/कड़बी) या अच्छी गुणवत्ता की घास जोड़ने से रूमेन का स्वास्थ्य और रेशे का संतुलन बेहतर होगा।</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Ang pagdaragdag ng kaunti pang tuyong pakain (dayami/tangkay ng mais) o de-kalidad na damo ay makatutulong sa mas malusog na rumen at balanse ng fiber.</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Menambahkan sedikit lebih banyak pakan kering (jerami padi/jerami jagung) atau rumput berkualitas tinggi akan mendukung kesehatan rumen dan keseimbangan serat.</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>การเพิ่มอาหารหยาบแห้ง (ฟางข้าว/ต้นข้าวโพดแห้ง) หรือหญ้าคุณภาพดีอีกเล็กน้อย จะช่วยให้กระเพาะรูเมนมีสุขภาพดีขึ้นและเยื่อใยสมดุลขึ้น</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Bổ sung thêm một ít thức ăn thô khô (rơm/thân cây ngô khô) hoặc cỏ chất lượng cao sẽ giúp dạ cỏ khỏe hơn và cân bằng xơ tốt hơn.</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>আরও কিছুটা শুকনো খাদ্য (খড়/ভুট্টার নাড়া) বা উন্নতমানের ঘাস যোগ করলে রুমেনের স্বাস্থ্য ও ফাইবারের ভারসাম্য ভালো থাকবে।</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>अलि बढी सुख्खा घाँस (पराल/ढोड) वा राम्रो गुणस्तरको घाँस थप्दा रुमेनको स्वास्थ्य र रेसाको सन्तुलन राम्रो हुन्छ।</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>ትንሽ ተጨማሪ ደረቅ መኖ (ገለባ/የበቆሎ አገዳ) ወይም ጥራት ያለው ሳር መጨመር የሩመንን (የመጀመሪያው ሆድ) ጤና እና የፋይበር ሚዛን ያሻሽላል።</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Nyaata gogaa (citaa/agadaa boqqolloo) ykn marga qulqullina olaanaa qabu xiqqoo dabaluun fayyaa garaa (rumen) fi madaallii faayibarii ni fooyyessa.</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>ቁሩብ ተወሳኺ ደረቕ መግቢ (ሓሰር/ሓሰር ዕፉን) ወይ ጽሬት ዘለዎ ሳዕሪ ምውሳኽ ጥዕና ሩመን (ቀዳማይ ከብዲ) ከምኡ'ውን ሚዛን ፋይበር ከመሓይሽ እዩ።</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>Ajouter un peu plus de fourrage sec (paille, tiges de maïs ou de sorgho) ou d'herbes de bonne qualité favoriserait la santé du rumen et l'équilibre en fibres.</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>إضافة قليل من العلف الجاف (التبن/حطب الذرة) أو أعشاب عالية الجودة ستدعم صحة الكرش وتوازن الألياف بشكل أفضل.</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Ƙara ɗan busasshen abinci (karmami/kara) ko ciyawa mai inganci zai taimaka wa lafiyar tumbi (rumen) da daidaiton zare.</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>Kuongeza kidogo malisho makavu (majani makavu/mabua ya mahindi) au nyasi bora kutasaidia afya ya tumbo kubwa (rumen) na mizani ya nyuzi.</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>Kũongerera hanini irio nyũmũ (mahuti momũ/mĩtĩ ya mbembe) kana nyeki njega nĩ gũgũteithia ũgima wa rumen (nda ya mbere) na mũiganĩro wa fibre.</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>ಸ್ವಲ್ಪ ಹೆಚ್ಚು ಒಣ ಮೇವು (ಒಣಹುಲ್ಲು/ಜೋಳದ ದಂಟು) ಅಥವಾ ಉತ್ತಮ ಗುಣಮಟ್ಟದ ಹುಲ್ಲನ್ನು ಸೇರಿಸಿದರೆ ರೂಮೆನ್ ಆರೋಗ್ಯ ಮತ್ತು ನಾರಿನ ಸಮತೋಲನ ಉತ್ತಮವಾಗುತ್ತದೆ.</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>சற்றுக் கூடுதலாக உலர் தீவனம் (வைக்கோல்/சோளத்தட்டை) அல்லது உயர்தரப் புற்களைச் சேர்த்தால் ருமென் ஆரோக்கியமும் நார்ச் சமநிலையும் மேம்படும்.</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>അല്പം കൂടി ഉണക്കത്തീറ്റ (വൈക്കോൽ/ചോളത്തണ്ട്) അല്ലെങ്കിൽ നല്ലയിനം പുല്ലുകൾ ചേർത്താൽ റൂമെന്റെ ആരോഗ്യവും നാരിന്റെ സന്തുലനവും മെച്ചപ്പെടും.</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>थोडा अधिक सुका चारा (काड/कडबा) किंवा चांगल्या प्रतीचे गवत घातल्यास कोठीपोटाचे (रुमेन) आरोग्य आणि तंतूंचे संतुलन सुधारेल.</t>
+        </is>
+      </c>
+      <c r="V170" s="2" t="inlineStr">
+        <is>
+          <t>కొంచెం ఎక్కువ ఎండు మేత (వరిగడ్డి/జొన్న చొప్ప) లేదా మంచి నాణ్యమైన గడ్డిని కలిపితే రూమెన్ ఆరోగ్యం మరియు పీచు సమతుల్యత మెరుగుపడతాయి.</t>
+        </is>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>થોડો વધુ સૂકો ચારો (પરાળ/કડબ) કે સારી ગુણવત્તાનું ઘાસ ઉમેરવાથી રૂમેનનું આરોગ્ય અને રેસાનું સંતુલન વધુ સારું રહેશે.</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>थोड़ो बेसी सूखो चारो (भूसो/कड़बी) या बढ़िया घास मिलावण सूं रूमेन री सेहत अर रेसा रो संतुलन चोखो रैवैला।</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr">
+        <is>
+          <t>ଆଉ ଟିକେ ଶୁଖିଲା ଚାରା (ପାଳ/ମକା ନଡ଼ା) କିମ୍ବା ଉନ୍ନତମାନର ଘାସ ମିଶାଇଲେ ରୁମେନର ସ୍ୱାସ୍ଥ୍ୟ ଓ ତନ୍ତୁ ସନ୍ତୁଳନ ଭଲ ରହିବ।</t>
+        </is>
+      </c>
+      <c r="Z170" s="2" t="inlineStr">
+        <is>
+          <t>ਥੋੜ੍ਹਾ ਹੋਰ ਸੁੱਕਾ ਚਾਰਾ (ਤੂੜੀ/ਕੜਬ) ਜਾਂ ਚੰਗੀ ਗੁਣਵੱਤਾ ਵਾਲਾ ਘਾਹ ਪਾਉਣ ਨਾਲ ਰੂਮਨ ਦੀ ਸਿਹਤ ਅਤੇ ਰੇਸ਼ੇ ਦਾ ਸੰਤੁਲਨ ਬਿਹਤਰ ਹੋਵੇਗਾ।</t>
+        </is>
+      </c>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>অলপ বেছি শুকান খাদ্য (খেৰ/মাকৈৰ ঠাৰি) বা উন্নত মানৰ ঘাঁহ যোগ কৰিলে ৰুমেনৰ স্বাস্থ্য আৰু আঁহৰ ভাৰসাম্য ভাল হ'ব।</t>
+        </is>
+      </c>
+      <c r="AB170" s="2" t="inlineStr">
+        <is>
+          <t>थोड़ा और सूखा चारा (तूड़ा/कड़बी) या बढ़िया घास मिलाण तै रूमेन की सेहत अर रेशे का संतुलन बढ़िया रहवैगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>The total fiber is slightly high. For better intake, you might consider replacing some low-quality straw with concentrates or fresh forage.</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>कुल रेशा थोड़ा अधिक है। पशु बेहतर खा सके, इसके लिए आप कुछ निम्न गुणवत्ता वाले भूसे की जगह दाना या हरा चारा देने पर विचार कर सकते हैं।</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Bahagyang mataas ang kabuuang fiber. Para mas makakain nang mabuti ang hayop, maaaring palitan ang bahagi ng mababang-kalidad na dayami ng concentrate o sariwang forage.</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Serat total sedikit tinggi. Agar konsumsi pakan lebih baik, Anda dapat mempertimbangkan mengganti sebagian jerami berkualitas rendah dengan konsentrat atau hijauan segar.</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>เยื่อใยทั้งหมดสูงไปเล็กน้อย เพื่อให้โคกินได้ดีขึ้น อาจพิจารณาแทนที่ฟางคุณภาพต่ำบางส่วนด้วยอาหารข้นหรืออาหารหยาบสด</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Tổng xơ hơi cao. Để bò ăn được nhiều hơn, bạn có thể cân nhắc thay một phần rơm chất lượng thấp bằng thức ăn tinh hoặc thức ăn thô xanh tươi.</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>মোট ফাইবার সামান্য বেশি। পশু যাতে ভালোভাবে খায়, সেজন্য কিছু নিম্নমানের খড়ের বদলে দানাদার খাদ্য বা তাজা সবুজ ঘাস দেওয়ার কথা ভাবতে পারেন।</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>जम्मा रेसा अलि बढी छ। पशुले राम्रोसँग खाओस् भनेर केही कम गुणस्तरको परालको सट्टा दाना वा हरियो घाँस दिने विचार गर्न सक्नुहुन्छ।</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>ጠቅላላ ፋይበር በትንሹ ከፍ ያለ ነው። እንስሳው የበለጠ እንዲመገብ፣ ዝቅተኛ ጥራት ያለውን ገለባ በከፊል በኮንሰንትሬት ወይም በእርጥብ ሻካራ መኖ መተካት ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>Faayibariin waliigalaa xiqqoo ol ka'eera. Akka horiin caalaatti nyaatuuf, citaa qulqullina gadaanaa qabu keessaa tokko tokko nyaata dabalataa ykn marga jiidhaatiin bakka buusuu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>ጠቕላላ ፋይበር ቁሩብ ልዑል እዩ። እንስሳ ብዝሓሸ ክበልዕ፣ ገለ ትሑት ጽሬት ዘለዎ ሓሰር ብኮንሰንትሬት ወይ ብጥረ ሳዕሪ ምትካእ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>Les fibres totales sont légèrement élevées. Pour une meilleure ingestion, vous pourriez remplacer une partie de la paille de faible qualité par des concentrés ou du fourrage vert.</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>إجمالي الألياف مرتفع قليلًا. لتحسين المأكول، يمكنك استبدال جزء من التبن منخفض الجودة بالمركزات أو بالعلف الأخضر الطازج.</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Jimlar zare ta ɗan yi yawa. Don dabbar ta fi cin abinci, za ku iya maye gurbin wani ɓangare na karmami mara inganci da abincin ƙari ko ɗanyar ciyawa.</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>Jumla ya nyuzi iko juu kidogo. Ili mnyama ale vizuri zaidi, unaweza kufikiria kubadilisha sehemu ya majani makavu duni kwa chakula cha nyongeza au malisho mabichi.</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>Fibre yothe nĩ nyingĩ hanini. Nĩguo nyamũ ĩrĩe wega makĩria, no ũcirie gũcenjia mahuti momũ mamwe matarĩ mega na irio cia kũongerera kana nyeki ĩrĩ nduru.</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>ಒಟ್ಟು ನಾರಿನ ಅಂಶ ಸ್ವಲ್ಪ ಹೆಚ್ಚಾಗಿದೆ. ಉತ್ತಮ ಸೇವನೆಗಾಗಿ, ಕಳಪೆ ಗುಣಮಟ್ಟದ ಒಣಹುಲ್ಲಿನ ಸ್ವಲ್ಪ ಭಾಗದ ಬದಲು ಸಾಂದ್ರ ಆಹಾರ ಅಥವಾ ಹಸಿರು ಮೇವನ್ನು ನೀಡುವುದನ್ನು ಪರಿಗಣಿಸಬಹುದು.</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>மொத்த நார் அளவு சற்று அதிகமாக உள்ளது. கால்நடை நன்றாக உண்ண, தரம் குறைந்த வைக்கோலின் ஒரு பகுதிக்குப் பதிலாக அடர் தீவனம் அல்லது பசுந்தீவனம் கொடுப்பதைக் கருதலாம்.</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>ആകെ നാരിന്റെ അളവ് അല്പം കൂടുതലാണ്. ഉരുക്കൾ നന്നായി തിന്നാൻ, ഗുണം കുറഞ്ഞ വൈക്കോലിന്റെ ഒരു ഭാഗത്തിനു പകരം സാന്ദ്രീകൃതാഹാരമോ പച്ചത്തീറ്റയോ നൽകുന്നത് പരിഗണിക്കാം.</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>एकूण तंतू थोडे जास्त आहेत. जनावराने चांगले खावे यासाठी काही निकृष्ट दर्जाच्या काडाऐवजी पशुखाद्य किंवा हिरवा चारा देण्याचा विचार करू शकता.</t>
+        </is>
+      </c>
+      <c r="V171" s="2" t="inlineStr">
+        <is>
+          <t>మొత్తం పీచు కొంచెం ఎక్కువగా ఉంది. పశువు బాగా తినడానికి, నాసిరకం వరిగడ్డిలో కొంత భాగానికి బదులుగా దాణా లేదా పచ్చి గ్రాసం ఇవ్వడం పరిశీలించవచ్చు.</t>
+        </is>
+      </c>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>કુલ રેસા થોડા વધારે છે. પશુ સારી રીતે ખાય તે માટે, તમે થોડા હલકી ગુણવત્તાના પરાળને બદલે દાણ કે તાજો લીલો ચારો આપવાનું વિચારી શકો.</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>कुल रेसो थोड़ो बेसी है। पशु चोखो खावै, इण खातर थोड़ा हल्का भूसा री जगां दाणो या हरो चारो देवण री सोच सको।</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr">
+        <is>
+          <t>ମୋଟ ତନ୍ତୁ ସାମାନ୍ୟ ଅଧିକ। ପଶୁ ଭଲ ଭାବେ ଖାଇବା ପାଇଁ, କିଛି ନିମ୍ନମାନର ପାଳ ବଦଳରେ ଦାନାଦାର ଖାଦ୍ୟ କିମ୍ବା ସତେଜ ସବୁଜ ଚାରା ଦେବା କଥା ବିଚାର କରିପାରନ୍ତି।</t>
+        </is>
+      </c>
+      <c r="Z171" s="2" t="inlineStr">
+        <is>
+          <t>ਕੁੱਲ ਰੇਸ਼ਾ ਥੋੜ੍ਹਾ ਵੱਧ ਹੈ। ਪਸ਼ੂ ਚੰਗੀ ਤਰ੍ਹਾਂ ਖਾਵੇ, ਇਸ ਲਈ ਤੁਸੀਂ ਕੁਝ ਘੱਟ ਗੁਣਵੱਤਾ ਵਾਲੀ ਤੂੜੀ ਦੀ ਥਾਂ ਦਾਣਾ ਜਾਂ ਤਾਜ਼ਾ ਹਰਾ ਚਾਰਾ ਦੇਣ ਬਾਰੇ ਸੋਚ ਸਕਦੇ ਹੋ।</t>
+        </is>
+      </c>
+      <c r="AA171" s="2" t="inlineStr">
+        <is>
+          <t>মুঠ আঁহ অলপ বেছি। পশুৱে ভালদৰে খাবৰ বাবে কিছু নিম্নমানৰ খেৰৰ সলনি দানাদাৰ খাদ্য বা কেঁচা সেউজীয়া ঘাঁহ দিয়াৰ কথা বিবেচনা কৰিব পাৰে।</t>
+        </is>
+      </c>
+      <c r="AB171" s="2" t="inlineStr">
+        <is>
+          <t>कुल रेशा थोड़ा घणा सै। पशु बढ़िया खावै, इस खातर थोड़े हल्के तूड़े की जगहां दाणा या हरा चारा देण की सोच सको सो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Starch content is a bit high. To maintain a healthy rumen, try slightly reducing cereal grains and increasing fiber-rich forages.</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>स्टार्च की मात्रा थोड़ी अधिक है। रूमेन को स्वस्थ रखने के लिए अनाज थोड़ा कम करें और रेशे से भरपूर चारा बढ़ाकर देखें।</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Bahagyang mataas ang starch. Para mapanatiling malusog ang rumen, subukang bawasan nang kaunti ang butil at dagdagan ang mga forage na mayaman sa fiber.</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Kadar pati sedikit tinggi. Untuk menjaga rumen tetap sehat, cobalah sedikit mengurangi biji-bijian dan menambah hijauan kaya serat.</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>ปริมาณแป้งสูงไปเล็กน้อย เพื่อรักษาสุขภาพกระเพาะรูเมน ลองลดเมล็ดธัญพืชลงเล็กน้อยและเพิ่มอาหารหยาบที่มีเยื่อใยสูง</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Hàm lượng tinh bột hơi cao. Để giữ dạ cỏ khỏe mạnh, hãy thử giảm bớt một chút hạt ngũ cốc và tăng thức ăn thô giàu xơ.</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>শ্বেতসারের পরিমাণ একটু বেশি। রুমেন সুস্থ রাখতে দানাশস্য সামান্য কমিয়ে আঁশসমৃদ্ধ খাদ্য বাড়িয়ে দেখুন।</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>स्टार्चको मात्रा अलि बढी छ। रुमेन स्वस्थ राख्न अन्न अलिकति घटाएर रेसायुक्त घाँस बढाएर हेर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>የስታርች መጠን ትንሽ ከፍ ያለ ነው። የሩመንን ጤና ለመጠበቅ፣ እህልን በትንሹ ቀንሰው በፋይበር የበለጸጉ ሻካራ መኖዎችን ይጨምሩ።</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Hammi istaarchii xiqqoo ol ka'eera. Fayyaa garaa (rumen) eeguuf, midhaan xiqqoo hir'isaa, marga faayibariin badhaadhe immoo dabalaa.</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>መጠን ስታርች ቁሩብ ልዑል እዩ። ጥዕና ሩመን ንምሕላው፣ እኽሊ ቁሩብ ቀንሱ፣ ብፋይበር ዝሃብተመ ሳዕሪ ድማ ወስኹ።</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>La teneur en amidon est un peu élevée. Pour garder un rumen sain, essayez de réduire légèrement les céréales et d'augmenter les fourrages riches en fibres.</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>محتوى النشا مرتفع بعض الشيء. للحفاظ على صحة الكرش، حاول تقليل الحبوب قليلًا وزيادة الأعلاف الخشنة الغنية بالألياف.</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Yawan sitaci ya ɗan yi yawa. Don kiyaye lafiyar tumbi (rumen), ku gwada rage hatsi kaɗan kuma ku ƙara ciyawa mai yawan zare.</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>Kiwango cha wanga kiko juu kidogo. Ili kudumisha afya ya tumbo kubwa (rumen), jaribu kupunguza nafaka kidogo na kuongeza malisho yenye nyuzi nyingi.</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>Starch nĩ nyingĩ hanini. Nĩguo rumen ĩtũũre ĩrĩ njega, geria kũnyihia ngano hanini na kũongerera nyeki ĩrĩ na fibre nyingĩ.</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>ಪಿಷ್ಟದ ಅಂಶ ಸ್ವಲ್ಪ ಹೆಚ್ಚಾಗಿದೆ. ರೂಮೆನ್ ಆರೋಗ್ಯವಾಗಿರಲು, ಧಾನ್ಯಗಳನ್ನು ಸ್ವಲ್ಪ ಕಡಿಮೆ ಮಾಡಿ ನಾರಿನಂಶ ಹೆಚ್ಚಿರುವ ಮೇವನ್ನು ಹೆಚ್ಚಿಸಿ ನೋಡಿ.</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>மாவுச்சத்து அளவு சற்று அதிகமாக உள்ளது. ருமென் ஆரோக்கியமாக இருக்க, தானியங்களைச் சற்றுக் குறைத்து நார்ச்சத்து மிகுந்த முரட்டுத் தீவனங்களை அதிகரித்துப் பாருங்கள்.</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>അന്നജത്തിന്റെ അളവ് അല്പം കൂടുതലാണ്. റൂമെൻ ആരോഗ്യത്തോടെ നിലനിർത്താൻ, ധാന്യങ്ങൾ അല്പം കുറച്ച് നാര് കൂടുതലുള്ള പരുഷാഹാരങ്ങൾ കൂട്ടി നോക്കുക.</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>स्टार्चचे प्रमाण थोडे जास्त आहे. कोठीपोट (रुमेन) निरोगी ठेवण्यासाठी धान्य थोडे कमी करा आणि तंतुमय चारा वाढवून पाहा.</t>
+        </is>
+      </c>
+      <c r="V172" s="2" t="inlineStr">
+        <is>
+          <t>పిండిపదార్థం కొంచెం ఎక్కువగా ఉంది. రూమెన్ ఆరోగ్యంగా ఉండటానికి, ధాన్యాలను కొంచెం తగ్గించి పీచు అధికంగా ఉండే గ్రాసాన్ని పెంచి చూడండి.</t>
+        </is>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>સ્ટાર્ચનું પ્રમાણ થોડું વધારે છે. રૂમેનને તંદુરસ્ત રાખવા માટે અનાજ થોડું ઘટાડી રેસાયુક્ત ઘાસચારો વધારી જુઓ.</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>स्टार्च री मात्रा थोड़ी बेसी है। रूमेन नै स्वस्थ राखण खातर अनाज थोड़ो घटाओ अर रेसा वालो चारो बधाय नै देखो।</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr">
+        <is>
+          <t>ଶ୍ୱେତସାର ପରିମାଣ ଟିକେ ଅଧିକ। ରୁମେନକୁ ସୁସ୍ଥ ରଖିବା ପାଇଁ ଶସ୍ୟ ଦାନା ସାମାନ୍ୟ କମାଇ ତନ୍ତୁଯୁକ୍ତ ଚାରା ବଢ଼ାଇ ଦେଖନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z172" s="2" t="inlineStr">
+        <is>
+          <t>ਨਿਸ਼ਾਸਤੇ ਦੀ ਮਾਤਰਾ ਥੋੜ੍ਹੀ ਵੱਧ ਹੈ। ਰੂਮਨ ਨੂੰ ਤੰਦਰੁਸਤ ਰੱਖਣ ਲਈ ਅਨਾਜ ਥੋੜ੍ਹਾ ਘਟਾ ਕੇ ਰੇਸ਼ੇ ਭਰਪੂਰ ਚਾਰਾ ਵਧਾ ਕੇ ਦੇਖੋ।</t>
+        </is>
+      </c>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>শ্বেতসাৰৰ পৰিমাণ অলপ বেছি। ৰুমেন সুস্থ ৰাখিবলৈ শস্যৰ দানা অলপ কমাই আঁহবহুল খাদ্য বঢ়াই চাওক।</t>
+        </is>
+      </c>
+      <c r="AB172" s="2" t="inlineStr">
+        <is>
+          <t>स्टार्च की मात्रा थोड़ी घणी सै। रूमेन नै ठीक राखण खातर अनाज थोड़ा घटाओ अर रेशे आला चारा बधा कै देखो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>The fat (EE) content is higher than the recommended limit. Reducing oil-rich seeds or supplements will help maintain optimal digestion.</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>वसा (EE) की मात्रा अनुशंसित सीमा से अधिक है। तेल वाले बीज (जैसे बिनौला) या पूरक कम करने से पाचन सही बना रहेगा।</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Ang taba (EE) ay mas mataas sa inirerekomendang limitasyon. Ang pagbabawas ng mga butong mayaman sa langis o ng mga supplement na may langis ay makatutulong upang mapanatili ang maayos na pagtunaw.</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Kadar lemak (EE) melebihi batas yang dianjurkan. Mengurangi biji-bijian berminyak atau suplemen kaya minyak akan membantu menjaga pencernaan tetap optimal.</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>ปริมาณไขมัน (EE) สูงกว่าขีดจำกัดที่แนะนำ การลดเมล็ดพืชน้ำมันหรืออาหารเสริมที่มีน้ำมันสูงจะช่วยให้การย่อยอาหารเป็นไปอย่างเหมาะสม</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Hàm lượng chất béo (EE) cao hơn giới hạn khuyến nghị. Giảm các loại hạt có dầu hoặc thức ăn bổ sung giàu dầu sẽ giúp duy trì tiêu hóa tốt.</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>ফ্যাটের (EE) পরিমাণ সুপারিশকৃত সীমার চেয়ে বেশি। তেলসমৃদ্ধ বীজ বা সম্পূরক খাদ্য কমালে হজম ভালো থাকবে।</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>चिल्लो (EE) को मात्रा सिफारिस गरिएको सीमाभन्दा बढी छ। तेल हुने बीउ (जस्तै कपासको बीउ) वा पूरक घटाउँदा पाचन राम्रो रहन्छ।</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>የቅባት (EE) መጠን ከሚመከረው ገደብ በላይ ነው። በዘይት የበለጸጉ ዘሮችን ወይም ተጨማሪዎችን መቀነስ ጥሩ የምግብ መፈጨትን ለመጠበቅ ይረዳል።</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>Hammi coomaa (EE) daangaa gorfame ol. Sanyii zayitiin badhaadhan ykn dabalata hir'isuun nyaanni sirriitti akka bulluqu eeguuf ni gargaara.</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>መጠን ስብሒ (EE) ካብቲ ዝተመኽረ ደረት ንላዕሊ እዩ። ብዘይቲ ዝሃብተሙ ፍረታት ወይ ተወሰኽቲ ምቕናስ ጽቡቕ ምሕቃቕ መግቢ ንምሕላው ይሕግዝ።</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>La teneur en matières grasses (EE) dépasse la limite recommandée. Réduire les graines oléagineuses ou les compléments gras aidera à maintenir une digestion optimale.</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>محتوى الدهن (EE) أعلى من الحد الموصى به. تقليل البذور الغنية بالزيت أو المكمّلات الزيتية سيساعد على الحفاظ على هضم مثالي.</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Yawan kitse (EE) ya wuce iyakar da aka ba da shawara. Rage iri masu yawan mai ko ƙarin abinci zai taimaka wajen kiyaye narkewar abinci yadda ya kamata.</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>Kiwango cha mafuta (EE) kiko juu ya kikomo kinachopendekezwa. Kupunguza mbegu zenye mafuta mengi au virutubisho kutasaidia kudumisha mmeng'enyo bora wa chakula.</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>Maguta (EE) nĩ maingĩ gũkĩra mũhaka ũrĩa ũtaarĩtwo. Kũnyihia mbegu irĩ na maguta maingĩ kana irio cia kũongerera nĩ gũgũteithia nda ĩgaye irio wega.</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>ಕೊಬ್ಬಿನ (EE) ಅಂಶ ಶಿಫಾರಸು ಮಾಡಿದ ಮಿತಿಗಿಂತ ಹೆಚ್ಚಾಗಿದೆ. ಎಣ್ಣೆಕಾಳುಗಳು ಅಥವಾ ಎಣ್ಣೆ ಸಮೃದ್ಧ ಪೂರಕಗಳನ್ನು ಕಡಿಮೆ ಮಾಡಿದರೆ ಉತ್ತಮ ಜೀರ್ಣಕ್ರಿಯೆ ಕಾಯ್ದುಕೊಳ್ಳಲು ಸಹಾಯವಾಗುತ್ತದೆ.</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>கொழுப்பு (EE) அளவு பரிந்துரைக்கப்பட்ட வரம்பை விட அதிகமாக உள்ளது. எண்ணெய் வித்துகள் அல்லது எண்ணெய் மிகுந்த துணைத் தீவனங்களைக் குறைத்தால் சீரான செரிமானத்தைப் பராமரிக்க உதவும்.</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>കൊഴുപ്പിന്റെ (EE) അളവ് ശുപാർശ ചെയ്ത പരിധിയേക്കാൾ കൂടുതലാണ്. എണ്ണക്കുരുക്കളോ എണ്ണ കൂടിയ അനുബന്ധങ്ങളോ കുറയ്ക്കുന്നത് മികച്ച ദഹനം നിലനിർത്താൻ സഹായിക്കും.</t>
+        </is>
+      </c>
+      <c r="U173" s="2" t="inlineStr">
+        <is>
+          <t>स्निग्धांशाचे (EE) प्रमाण शिफारस केलेल्या मर्यादेपेक्षा जास्त आहे. तेलबिया (उदा. सरकी) किंवा पूरक खाद्य कमी केल्यास पचन चांगले राहील.</t>
+        </is>
+      </c>
+      <c r="V173" s="2" t="inlineStr">
+        <is>
+          <t>కొవ్వు (EE) శాతం సిఫార్సు చేసిన పరిమితి కంటే ఎక్కువగా ఉంది. నూనె గింజలు లేదా నూనె అధికంగా ఉండే అనుబంధాలను తగ్గిస్తే జీర్ణక్రియ సరిగ్గా కొనసాగుతుంది.</t>
+        </is>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>ચરબી (EE)નું પ્રમાણ ભલામણ કરેલી મર્યાદા કરતાં વધારે છે. તેલવાળાં બીજ કે પૂરક ઘટાડવાથી પાચન સારું રાખવામાં મદદ મળશે.</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>वसा (EE) री मात्रा सिफारिश करी सीमा सूं बेसी है। तेल वाला बीज (जियां बिनौला) या पूरक घटावण सूं पाचन सही रैवैला।</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr">
+        <is>
+          <t>ଚର୍ବି (EE) ପରିମାଣ ସୁପାରିଶ କରାଯାଇଥିବା ସୀମାଠାରୁ ଅଧିକ। ତେଲଯୁକ୍ତ ମଞ୍ଜି କିମ୍ବା ପରିପୂରକ କମାଇଲେ ହଜମ ଭଲ ରହିବାରେ ସାହାଯ୍ୟ ହେବ।</t>
+        </is>
+      </c>
+      <c r="Z173" s="2" t="inlineStr">
+        <is>
+          <t>ਚਰਬੀ (EE) ਦੀ ਮਾਤਰਾ ਸਿਫ਼ਾਰਸ਼ ਕੀਤੀ ਹੱਦ ਤੋਂ ਵੱਧ ਹੈ। ਤੇਲ ਵਾਲੇ ਬੀਜ ਜਾਂ ਪੂਰਕ ਘਟਾਉਣ ਨਾਲ ਹਾਜ਼ਮਾ ਠੀਕ ਰੱਖਣ ਵਿੱਚ ਮਦਦ ਮਿਲੇਗੀ।</t>
+        </is>
+      </c>
+      <c r="AA173" s="2" t="inlineStr">
+        <is>
+          <t>চৰ্বিৰ (EE) পৰিমাণ পৰামৰ্শ দিয়া সীমাতকৈ বেছি। তেলযুক্ত বীজ বা পৰিপূৰক খাদ্য কমালে হজম ভালদৰে হোৱাত সহায় হ'ব।</t>
+        </is>
+      </c>
+      <c r="AB173" s="2" t="inlineStr">
+        <is>
+          <t>वसा (EE) की मात्रा सिफारिश करी होई सीमा तै घणी सै। तेल आले बीज (जिसे बिनौला) या पूरक घटाण तै पाचन ठीक रहवैगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Ash content is a bit high. Checking the quality and cleanliness of your forages can help reduce this to ideal levels.</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>राख की मात्रा थोड़ी अधिक है। अपने चारे की गुणवत्ता और साफ़-सफ़ाई (मिट्टी-धूल) की जाँच करने से इसे आदर्श स्तर तक लाने में मदद मिल सकती है।</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Bahagyang mataas ang abo. Ang pagsuri sa kalidad at kalinisan ng inyong forage ay makatutulong upang maibaba ito sa tamang antas.</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Kadar abu sedikit tinggi. Memeriksa kualitas dan kebersihan hijauan Anda dapat membantu menurunkannya ke tingkat ideal.</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>ปริมาณเถ้าสูงไปเล็กน้อย การตรวจสอบคุณภาพและความสะอาดของอาหารหยาบจะช่วยลดเถ้าให้อยู่ในระดับที่เหมาะสม</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Hàm lượng tro hơi cao. Kiểm tra chất lượng và độ sạch của thức ăn thô có thể giúp giảm tro về mức lý tưởng.</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>ছাইয়ের পরিমাণ একটু বেশি। আপনার আঁশজাতীয় খাদ্যের মান ও পরিচ্ছন্নতা যাচাই করলে এটি আদর্শ মাত্রায় কমিয়ে আনা যেতে পারে।</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>खरानीको मात्रा अलि बढी छ। घाँसको गुणस्तर र सफाइ (माटो-धुलो) जाँच गर्दा यसलाई आदर्श स्तरमा ल्याउन मद्दत पुग्छ।</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>የአመድ መጠን ትንሽ ከፍ ያለ ነው። የሻካራ መኖዎችዎን ጥራት እና ንጽሕና መፈተሽ ይህንን ወደ ተገቢው ደረጃ ለመቀነስ ይረዳል።</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Hammi daaraa xiqqoo ol ka'eera. Qulqullinaa fi qulqullummaa marga keessanii mirkaneessuun sadarkaa sirriitti hir'isuuf ni gargaara.</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>መጠን ሓሙኽሽቲ ቁሩብ ልዑል እዩ። ጽሬትን ጽርየትን ሳዕርኹም ምፍታሽ ናብ ቅኑዕ ደረጃ ንምንካዩ ክሕግዝ ይኽእል።</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>La teneur en cendres est un peu élevée. Vérifier la qualité et la propreté de vos fourrages peut aider à la ramener à un niveau idéal.</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>محتوى الرماد مرتفع بعض الشيء. التحقق من جودة الأعلاف الخشنة ونظافتها يمكن أن يساعد على خفضه إلى المستويات المثالية.</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Yawan toka ya ɗan yi yawa. Duba inganci da tsabtar ciyawarku zai iya taimakawa wajen rage shi zuwa matakin da ya dace.</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>Kiwango cha majivu kiko juu kidogo. Kuangalia ubora na usafi wa malisho yako kunaweza kusaidia kukipunguza hadi kiwango bora.</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>Mũhu nĩ mũingĩ hanini. Gũthuthuria wega na ũtheru wa nyeki yaku no gũteithie kũnyihia mũhu ũkinye kĩgero kĩagĩrĩire.</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>ಬೂದಿ ಅಂಶ ಸ್ವಲ್ಪ ಹೆಚ್ಚಾಗಿದೆ. ನಿಮ್ಮ ಮೇವಿನ ಗುಣಮಟ್ಟ ಮತ್ತು ಸ್ವಚ್ಛತೆಯನ್ನು ಪರಿಶೀಲಿಸಿದರೆ ಇದನ್ನು ಆದರ್ಶ ಮಟ್ಟಕ್ಕೆ ಇಳಿಸಲು ಸಹಾಯವಾಗುತ್ತದೆ.</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>சாம்பல் அளவு சற்று அதிகமாக உள்ளது. உங்கள் முரட்டுத் தீவனங்களின் தரத்தையும் சுத்தத்தையும் சரிபார்த்தால் இதைச் சிறந்த அளவுக்குக் குறைக்க உதவும்.</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>ചാരത്തിന്റെ അളവ് അല്പം കൂടുതലാണ്. നിങ്ങളുടെ പരുഷാഹാരങ്ങളുടെ ഗുണനിലവാരവും വൃത്തിയും പരിശോധിക്കുന്നത് ഇത് അനുയോജ്യമായ നിലയിലേക്ക് കുറയ്ക്കാൻ സഹായിക്കും.</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>राखेचे प्रमाण थोडे जास्त आहे. तुमच्या चाऱ्याचा दर्जा आणि स्वच्छता (माती-धूळ) तपासल्यास हे आदर्श पातळीवर आणण्यास मदत होईल.</t>
+        </is>
+      </c>
+      <c r="V174" s="2" t="inlineStr">
+        <is>
+          <t>బూడిద శాతం కొంచెం ఎక్కువగా ఉంది. మీ గ్రాసం నాణ్యతను, శుభ్రతను పరిశీలిస్తే దీన్ని సరైన స్థాయికి తగ్గించవచ్చు.</t>
+        </is>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>રાખનું પ્રમાણ થોડું વધારે છે. તમારા ઘાસચારાની ગુણવત્તા અને સ્વચ્છતા તપાસવાથી તેને આદર્શ સ્તરે ઘટાડવામાં મદદ મળી શકે.</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>राख री मात्रा थोड़ी बेसी है। थारा चारा री गुणवत्ता अर साफ-सफाई (माटी-धूल) जांचण सूं इणनै आदर्श स्तर तांई लावण में मदद मिलैला।</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr">
+        <is>
+          <t>ପାଉଁଶ ପରିମାଣ ଟିକେ ଅଧିକ। ଆପଣଙ୍କ ଚାରାର ଗୁଣବତ୍ତା ଓ ପରିଷ୍କାରତା ଯାଞ୍ଚ କଲେ ଏହାକୁ ଆଦର୍ଶ ମାତ୍ରାକୁ କମାଇବାରେ ସାହାଯ୍ୟ ମିଳିପାରେ।</t>
+        </is>
+      </c>
+      <c r="Z174" s="2" t="inlineStr">
+        <is>
+          <t>ਸੁਆਹ ਦੀ ਮਾਤਰਾ ਥੋੜ੍ਹੀ ਵੱਧ ਹੈ। ਆਪਣੇ ਚਾਰੇ ਦੀ ਗੁਣਵੱਤਾ ਅਤੇ ਸਫ਼ਾਈ ਦੀ ਜਾਂਚ ਕਰਨ ਨਾਲ ਇਸ ਨੂੰ ਆਦਰਸ਼ ਪੱਧਰ ਤੱਕ ਘਟਾਉਣ ਵਿੱਚ ਮਦਦ ਮਿਲ ਸਕਦੀ ਹੈ।</t>
+        </is>
+      </c>
+      <c r="AA174" s="2" t="inlineStr">
+        <is>
+          <t>ছাইৰ পৰিমাণ অলপ বেছি। আপোনাৰ আঁহযুক্ত খাদ্যৰ মান আৰু পৰিষ্কাৰ-পৰিচ্ছন্নতা পৰীক্ষা কৰিলে ইয়াক আদৰ্শ মাত্ৰালৈ কমাব পাৰি।</t>
+        </is>
+      </c>
+      <c r="AB174" s="2" t="inlineStr">
+        <is>
+          <t>राख की मात्रा थोड़ी घणी सै। अपणे चारे की गुणवत्ता अर साफ-सफाई (माट्टी-धूल) जांचण तै इसनै आदर्श स्तर ताईं ल्याण म्ह मदद मिलैगी।</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>To maintain a cost-effective and healthy balance, you might consider slightly increasing the forage proportion relative to concentrates.</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>किफायती और स्वस्थ संतुलन बनाए रखने के लिए आप दाने की तुलना में चारे का अनुपात थोड़ा बढ़ाने पर विचार कर सकते हैं।</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Para mapanatili ang balanseng matipid at malusog, maaaring bahagyang dagdagan ang proporsyon ng forage kumpara sa concentrate.</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Untuk menjaga keseimbangan yang hemat biaya dan sehat, Anda dapat mempertimbangkan sedikit menambah proporsi hijauan dibandingkan konsentrat.</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>เพื่อรักษาสมดุลที่คุ้มค่าและดีต่อสุขภาพ อาจพิจารณาเพิ่มสัดส่วนอาหารหยาบเมื่อเทียบกับอาหารข้นเล็กน้อย</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Để duy trì sự cân bằng tiết kiệm chi phí và tốt cho sức khỏe, bạn có thể cân nhắc tăng nhẹ tỷ lệ thức ăn thô so với thức ăn tinh.</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>খরচ-সাশ্রয়ী ও স্বাস্থ্যকর ভারসাম্য বজায় রাখতে দানাদার খাদ্যের তুলনায় আঁশজাতীয় খাদ্যের অনুপাত সামান্য বাড়ানোর কথা ভাবতে পারেন।</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>कम खर्चिलो र स्वस्थ सन्तुलन कायम राख्न तपाईं दानाको तुलनामा घाँसको अनुपात अलिकति बढाउने विचार गर्न सक्नुहुन्छ।</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>ወጪ ቆጣቢ እና ጤናማ ሚዛን ለመጠበቅ፣ ከኮንሰንትሬት አንጻር የሻካራ መኖን ድርሻ በትንሹ መጨመር ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Madaallii baasii qusatu fi fayyaa qabu eeguuf, qooda margaa nyaata dabalataa wajjin yoo walbira qabamu xiqqoo dabaluu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>ቁጠባውን ጥዑይን ሚዛን ንምሕላው፣ ብጽሒት ሳዕሪ ምስ ኮንሰንትሬት ብምንጽጻር ቁሩብ ምውሳኽ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>Pour garder un équilibre sain et économique, vous pourriez augmenter légèrement la part de fourrage par rapport aux concentrés.</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>للحفاظ على توازن صحي واقتصادي، يمكنك زيادة نسبة العلف الخشن قليلًا مقارنة بالمركزات.</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Don kiyaye daidaito mai araha kuma mai lafiya, za ku iya ɗan ƙara yawan ciyawa idan aka kwatanta da abincin ƙari.</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>Ili kudumisha mizani yenye gharama nafuu na afya, unaweza kufikiria kuongeza kidogo sehemu ya malisho ukilinganisha na chakula cha nyongeza.</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>Nĩguo ũtũũrie mũiganĩro wa thogora mũnini na ũgima, no ũcirie kũongerera hanini gĩcunjĩ kĩa nyeki kũringana na irio cia kũongerera.</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>ಕಡಿಮೆ ವೆಚ್ಚದ ಮತ್ತು ಆರೋಗ್ಯಕರ ಸಮತೋಲನ ಕಾಯ್ದುಕೊಳ್ಳಲು, ಸಾಂದ್ರ ಆಹಾರಕ್ಕೆ ಹೋಲಿಸಿದರೆ ಮೇವಿನ ಪ್ರಮಾಣವನ್ನು ಸ್ವಲ್ಪ ಹೆಚ್ಚಿಸುವುದನ್ನು ಪರಿಗಣಿಸಬಹುದು.</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>குறைந்த செலவிலும் ஆரோக்கியமாகவும் சமநிலையைப் பராமரிக்க, அடர் தீவனத்துடன் ஒப்பிடுகையில் முரட்டுத் தீவனத்தின் விகிதத்தைச் சற்று அதிகரிப்பதைக் கருதலாம்.</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>ചെലവ് കുറഞ്ഞതും ആരോഗ്യകരവുമായ സന്തുലനം നിലനിർത്താൻ, സാന്ദ്രീകൃതാഹാരത്തെ അപേക്ഷിച്ച് പരുഷാഹാരത്തിന്റെ അനുപാതം അല്പം കൂട്ടുന്നത് പരിഗണിക്കാം.</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>किफायतशीर आणि निरोगी संतुलन राखण्यासाठी तुम्ही पशुखाद्याच्या तुलनेत चाऱ्याचे प्रमाण थोडे वाढवण्याचा विचार करू शकता.</t>
+        </is>
+      </c>
+      <c r="V175" s="2" t="inlineStr">
+        <is>
+          <t>తక్కువ ఖర్చుతో ఆరోగ్యకరమైన సమతుల్యత కోసం, దాణాతో పోలిస్తే గ్రాసం నిష్పత్తిని కొంచెం పెంచడం పరిశీలించవచ్చు.</t>
+        </is>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>ઓછા ખર્ચે તંદુરસ્ત સંતુલન જાળવવા માટે, તમે દાણની સરખામણીમાં ઘાસચારાનું પ્રમાણ થોડું વધારવાનું વિચારી શકો.</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>सस्तो अर स्वस्थ संतुलन राखण खातर थे दाणा री तुलना में चारा रो अनुपात थोड़ो बधावण री सोच सको।</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>କମ୍ ଖର୍ଚ୍ଚରେ ସୁସ୍ଥ ସନ୍ତୁଳନ ବଜାୟ ରଖିବା ପାଇଁ ଦାନାଦାର ଖାଦ୍ୟ ତୁଳନାରେ ଚାରାର ଅନୁପାତ ସାମାନ୍ୟ ବଢ଼ାଇବା କଥା ବିଚାର କରିପାରନ୍ତି।</t>
+        </is>
+      </c>
+      <c r="Z175" s="2" t="inlineStr">
+        <is>
+          <t>ਘੱਟ ਖ਼ਰਚੇ ਵਾਲਾ ਅਤੇ ਸਿਹਤਮੰਦ ਸੰਤੁਲਨ ਬਣਾਈ ਰੱਖਣ ਲਈ ਤੁਸੀਂ ਦਾਣੇ ਦੇ ਮੁਕਾਬਲੇ ਚਾਰੇ ਦਾ ਹਿੱਸਾ ਥੋੜ੍ਹਾ ਵਧਾਉਣ ਬਾਰੇ ਸੋਚ ਸਕਦੇ ਹੋ।</t>
+        </is>
+      </c>
+      <c r="AA175" s="2" t="inlineStr">
+        <is>
+          <t>কম খৰচী আৰু স্বাস্থ্যকৰ ভাৰসাম্য বজাই ৰাখিবলৈ দানাদাৰ খাদ্যৰ তুলনাত আঁহযুক্ত খাদ্যৰ অনুপাত অলপ বঢ়োৱাৰ কথা বিবেচনা কৰিব পাৰে।</t>
+        </is>
+      </c>
+      <c r="AB175" s="2" t="inlineStr">
+        <is>
+          <t>सस्ता अर ठीक संतुलन राखण खातर थम दाणे के मुकाबले चारे का अनुपात थोड़ा बधाण की सोच सको सो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Consider improving the forage quality by adding more legumes or silage to reach a more optimal balance.</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>बेहतर संतुलन के लिए अधिक फलीदार चारा या साइलेज जोड़कर चारे की गुणवत्ता सुधारने पर विचार करें।</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Maaaring pagbutihin ang kalidad ng forage sa pamamagitan ng pagdaragdag ng mas maraming legume o silage upang makamit ang mas mainam na balanse.</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Pertimbangkan untuk meningkatkan kualitas hijauan dengan menambah leguminosa atau silase agar keseimbangan lebih optimal.</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>ควรพิจารณาปรับปรุงคุณภาพอาหารหยาบโดยเพิ่มพืชตระกูลถั่วหรือพืชหมักให้มากขึ้น เพื่อให้ได้สมดุลที่เหมาะสมยิ่งขึ้น</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Bạn nên cân nhắc nâng cao chất lượng thức ăn thô bằng cách bổ sung thêm cây họ đậu hoặc thức ăn ủ chua để đạt sự cân bằng tốt hơn.</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>আরও উপযুক্ত ভারসাম্যে পৌঁছাতে বেশি শিম্বজাতীয় ঘাস বা সাইলেজ যোগ করে আঁশজাতীয় খাদ্যের মান উন্নত করার কথা ভাবুন।</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>अझ राम्रो सन्तुलनमा पुग्न बढी कोसे घाँस वा साइलेज थपेर घाँसको गुणस्तर सुधार गर्ने विचार गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>የተሻለ ሚዛን ለማግኘት፣ ተጨማሪ የጥራጥሬ መኖ ወይም ሲላጅ በመጨመር የሻካራ መኖን ጥራት ማሻሻል ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Madaallii caalaa ga'uuf, nyaata gosa ataraa ykn silaajii dabaluun qulqullina margaa fooyyessuu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>ዝሓሸ ሚዛን ንምብጻሕ፣ ተወሳኺ ጥረ-ኣእካል መግቢ ወይ ሲላጅ ብምውሳኽ ጽሬት ሳዕሪ ምምሕያሽ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>Pensez à améliorer la qualité du fourrage en ajoutant plus de légumineuses ou d'ensilage pour atteindre un meilleur équilibre.</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>يُنصح بتحسين جودة العلف الخشن بإضافة مزيد من البقوليات أو السيلاج لبلوغ توازن أفضل.</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Ku yi la'akari da inganta ciyawa ta hanyar ƙara harawa ko silage (ciyawar da aka adana) don samun daidaito mafi kyau.</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>Fikiria kuboresha ubora wa malisho kwa kuongeza mikunde zaidi au sileji ili kufikia mizani bora zaidi.</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>Ciria kwagĩria nyeki na kũongerera mĩmera ya mũthemba wa mboco kana silage nĩguo ũkinye mũiganĩro mwega makĩria.</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>ಹೆಚ್ಚು ಸೂಕ್ತ ಸಮತೋಲನ ತಲುಪಲು, ಹೆಚ್ಚು ದ್ವಿದಳ ಮೇವು ಅಥವಾ ರಸಮೇವು (ಸೈಲೇಜ್) ಸೇರಿಸಿ ಮೇವಿನ ಗುಣಮಟ್ಟವನ್ನು ಸುಧಾರಿಸುವುದನ್ನು ಪರಿಗಣಿಸಿ.</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>மேலும் உகந்த சமநிலையை அடைய, கூடுதல் பயறுவகைத் தீவனங்கள் அல்லது ஊறுகாய்ப் புல் (சைலேஜ்) சேர்த்து முரட்டுத் தீவனத்தின் தரத்தை மேம்படுத்துவதைக் கருதுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>കൂടുതൽ അനുയോജ്യമായ സന്തുലനത്തിലെത്താൻ, കൂടുതൽ പയർവർഗ്ഗ തീറ്റകളോ സൈലേജോ ചേർത്ത് പരുഷാഹാരത്തിന്റെ ഗുണനിലവാരം മെച്ചപ്പെടുത്തുന്നത് പരിഗണിക്കുക.</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>अधिक चांगले संतुलन साधण्यासाठी जास्त द्विदल चारा किंवा मुरघास (सायलेज) घालून चाऱ्याचा दर्जा सुधारण्याचा विचार करा.</t>
+        </is>
+      </c>
+      <c r="V176" s="2" t="inlineStr">
+        <is>
+          <t>మరింత సరైన సమతుల్యత కోసం, ఎక్కువ పప్పుజాతి గ్రాసం లేదా సైలేజ్ (పాతర గడ్డి) కలిపి గ్రాసం నాణ్యతను మెరుగుపరచడం పరిశీలించండి.</t>
+        </is>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>વધુ યોગ્ય સંતુલન મેળવવા માટે વધુ કઠોળવર્ગીય ચારો કે સાઇલેજ ઉમેરીને ઘાસચારાની ગુણવત્તા સુધારવાનું વિચારો.</t>
+        </is>
+      </c>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>बेहतर संतुलन खातर बेसी फलीदार चारो या साइलेज मिलाय नै चारा री गुणवत्ता सुधारण री सोचो।</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr">
+        <is>
+          <t>ଅଧିକ ଉପଯୁକ୍ତ ସନ୍ତୁଳନ ପାଇଁ ଅଧିକ ଡାଲିଜାତୀୟ ଚାରା କିମ୍ବା ସାଇଲେଜ୍ ମିଶାଇ ଚାରାର ଗୁଣବତ୍ତା ଉନ୍ନତ କରିବା କଥା ବିଚାର କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z176" s="2" t="inlineStr">
+        <is>
+          <t>ਵਧੇਰੇ ਢੁਕਵਾਂ ਸੰਤੁਲਨ ਹਾਸਲ ਕਰਨ ਲਈ ਵੱਧ ਫਲੀਦਾਰ ਚਾਰਾ ਜਾਂ ਸਾਈਲੇਜ (ਆਚਾਰ) ਪਾ ਕੇ ਚਾਰੇ ਦੀ ਗੁਣਵੱਤਾ ਸੁਧਾਰਨ ਬਾਰੇ ਸੋਚੋ।</t>
+        </is>
+      </c>
+      <c r="AA176" s="2" t="inlineStr">
+        <is>
+          <t>অধিক উপযুক্ত ভাৰসাম্যৰ বাবে বেছিকৈ মাহজাতীয় ঘাঁহ বা চাইলেজ যোগ কৰি আঁহযুক্ত খাদ্যৰ মান উন্নত কৰাৰ কথা বিবেচনা কৰক।</t>
+        </is>
+      </c>
+      <c r="AB176" s="2" t="inlineStr">
+        <is>
+          <t>बढ़िया संतुलन खातर और फलीदार चारा या साइलेज मिला कै चारे की गुणवत्ता सुधारण की सोचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Very wet ingredients make up more of the diet than ideal. Replacing part of them with a drier alternative will help dry matter intake and keep the ration stable.</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>आहार में बहुत गीले घटक आदर्श से अधिक हैं। इनके कुछ हिस्से की जगह कोई सूखा विकल्प देने से शुष्क पदार्थ सेवन बेहतर होगा और राशन स्थिर रहेगा।</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Mas malaki kaysa nararapat ang bahagi ng mga napakabasang sangkap sa rasyon. Ang pagpapalit ng bahagi nito ng mas tuyong alternatibo ay makatutulong sa dry matter intake at mapanatiling matatag ang rasyon.</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Bahan yang sangat basah mengisi porsi ransum lebih besar dari yang ideal. Mengganti sebagian dengan bahan yang lebih kering akan membantu konsumsi bahan kering dan menjaga ransum tetap stabil.</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>วัตถุดิบที่เปียกมากมีสัดส่วนในสูตรอาหารมากกว่าที่เหมาะสม การแทนที่บางส่วนด้วยวัตถุดิบที่แห้งกว่าจะช่วยให้โคกินวัตถุแห้งได้ดีขึ้นและทำให้สูตรอาหารคงที่</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Các nguyên liệu quá ướt đang chiếm tỷ lệ trong khẩu phần cao hơn mức lý tưởng. Thay một phần bằng nguyên liệu khô hơn sẽ giúp tăng lượng chất khô ăn vào và giữ khẩu phần ổn định.</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>খুব ভেজা উপকরণ খাদ্য তালিকার আদর্শের চেয়ে বেশি অংশ জুড়ে আছে। এর কিছু অংশ শুকনো বিকল্প দিয়ে বদলালে শুষ্ক পদার্থ গ্রহণ ভালো হবে এবং রেশন স্থিতিশীল থাকবে।</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>आहारमा धेरै भिजेका घटक आदर्शभन्दा बढी छन्। तीमध्ये केही भागको सट्टा सुख्खा विकल्प दिँदा सुख्खा पदार्थ सेवन राम्रो हुन्छ र आहार स्थिर रहन्छ।</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>በጣም እርጥብ መኖዎች ከሚገባው በላይ የራሽኑን ድርሻ ይይዛሉ። ከፊሉን በደረቅ አማራጭ መተካት የደረቅ ነገር ቅበላን ያሻሽላል፣ ራሽኑንም የተረጋጋ ያደርጋል።</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Nyaanni baay'ee jiidhaan nyaata keessaa qooda sirrii ol qaba. Isaan keessaa tokko tokko nyaata gogaatiin bakka buusuun nyaata gogaa fudhatamu ni gargaara, nyaatas tasgabbeessa.</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>ኣዝዮም ርሑሳት መግብታት ካብቲ ዝግባእ ንላዕሊ ብጽሒት ካብ መግቢ ሒዞም ኣለዉ። ገለ ካባታቶም ብዝነቐጸ መግቢ ምትካእ ምብላዕ ደረቕ ነገር ይሕግዝ፣ መግቢ ድማ ርጉእ ይገብሮ።</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>Les aliments très humides représentent une part de la ration plus élevée que l'idéal. En remplacer une partie par un aliment plus sec favorisera l'ingestion de matière sèche et la stabilité de la ration.</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>المكونات الرطبة جدًا تشكل جزءًا من العليقة أكبر من المثالي. استبدال جزء منها ببديل أكثر جفافًا سيساعد على زيادة المأكول من المادة الجافة ويحافظ على ثبات العليقة.</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Abinci mai ruwa sosai ya fi yawa a cikin abincin fiye da yadda ya dace. Maye gurbin wani ɓangare da busasshen abinci zai taimaka wajen cin busasshen abinci kuma ya sa abincin ya tsaya daidai.</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>Vyakula vyenye maji mengi sana ni sehemu kubwa ya lishe kuliko inavyofaa. Kubadilisha sehemu yake kwa chakula kikavu zaidi kutasaidia ulaji wa chakula kikavu na kuifanya lishe iwe thabiti.</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>Irio irĩ na maaĩ maingĩ mũno nĩ nyingĩ thĩinĩ wa irio gũkĩra kĩrĩa kĩagĩrĩire. Gũcenjia imwe ciacio na irio nyũmũ nĩ gũgũteithia kũrĩa irio nyũmũ na gũtũũria irio iiganĩire.</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>ತುಂಬಾ ತೇವಾಂಶವಿರುವ ಪದಾರ್ಥಗಳು ಆಹಾರದಲ್ಲಿ ಇರಬೇಕಾದುದಕ್ಕಿಂತ ಹೆಚ್ಚು ಪಾಲು ಹೊಂದಿವೆ. ಅವುಗಳ ಒಂದು ಭಾಗದ ಬದಲು ಒಣ ಪರ್ಯಾಯವನ್ನು ನೀಡಿದರೆ ಒಣ ಪದಾರ್ಥ ಸೇವನೆ ಸುಧಾರಿಸುತ್ತದೆ ಮತ್ತು ಪಡಿತರ ಸ್ಥಿರವಾಗಿರುತ್ತದೆ.</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>மிகவும் ஈரமான பொருட்கள் தீவனத்தில் தேவைக்கு அதிகமான பங்கு வகிக்கின்றன. அவற்றில் ஒரு பகுதிக்குப் பதிலாக உலர்ந்த மாற்றுப் பொருளைக் கொடுத்தால் உலர் பொருள் உட்கொள்ளல் மேம்படும், தீவனமும் நிலையாக இருக்கும்.</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr">
+        <is>
+          <t>വളരെ ഈർപ്പമുള്ള ചേരുവകൾ തീറ്റയിൽ വേണ്ടതിലധികം ഉണ്ട്. അവയുടെ ഒരു ഭാഗത്തിനു പകരം ഈർപ്പം കുറഞ്ഞ മറ്റൊന്ന് നൽകുന്നത് ശുഷ്ക പദാർത്ഥ ഉപഭോഗം മെച്ചപ്പെടുത്താനും തീറ്റ സ്ഥിരമായി നിലനിർത്താനും സഹായിക്കും.</t>
+        </is>
+      </c>
+      <c r="U177" s="2" t="inlineStr">
+        <is>
+          <t>आहारात खूप ओल्या घटकांचे प्रमाण आदर्शापेक्षा जास्त आहे. त्यांच्या काही भागाऐवजी कोरडा पर्याय दिल्यास शुष्क पदार्थ सेवन सुधारेल आणि आहार स्थिर राहील.</t>
+        </is>
+      </c>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>బాగా తడిగా ఉండే పదార్థాలు ఆహారంలో అవసరానికి మించి ఉన్నాయి. వాటిలో కొంత భాగానికి బదులుగా పొడిగా ఉండే ప్రత్యామ్నాయాన్ని ఇస్తే పొడి పదార్థం తీసుకోవడం మెరుగుపడుతుంది, రేషన్ స్థిరంగా ఉంటుంది.</t>
+        </is>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>ખૂબ ભીના ઘટકો આહારનો આદર્શ કરતાં વધુ ભાગ બનાવે છે. તેમાંથી થોડો ભાગ સૂકા વિકલ્પથી બદલવાથી સૂકા પદાર્થનો વપરાશ સુધરશે અને રાશન સ્થિર રહેશે.</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>आहार में घणा गीला घटक आदर्श सूं बेसी है। इणां रो कीं हिस्सो सूखा विकल्प सूं बदलण सूं शुष्क पदार्थ सेवन चोखो होवैला अर आहार स्थिर रैवैला।</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>ଅତ୍ୟଧିକ ଓଦା ଉପାଦାନ ଖାଦ୍ୟର ଆଦର୍ଶଠାରୁ ଅଧିକ ଅଂଶ ନେଇଛି। ଏହାର କିଛି ଅଂଶ ଶୁଖିଲା ବିକଳ୍ପରେ ବଦଳାଇଲେ ଶୁଷ୍କ ପଦାର୍ଥ ଗ୍ରହଣ ଭଲ ହେବ ଏବଂ ରାସନ ସ୍ଥିର ରହିବ।</t>
+        </is>
+      </c>
+      <c r="Z177" s="2" t="inlineStr">
+        <is>
+          <t>ਬਹੁਤ ਗਿੱਲੇ ਪਦਾਰਥ ਖੁਰਾਕ ਦਾ ਆਦਰਸ਼ ਨਾਲੋਂ ਵੱਧ ਹਿੱਸਾ ਬਣਦੇ ਹਨ। ਇਨ੍ਹਾਂ ਦਾ ਕੁਝ ਹਿੱਸਾ ਕਿਸੇ ਸੁੱਕੇ ਬਦਲ ਨਾਲ ਬਦਲਣ ਨਾਲ ਖ਼ੁਸ਼ਕ ਪਦਾਰਥ ਦੀ ਖਪਤ ਵਿੱਚ ਮਦਦ ਮਿਲੇਗੀ ਅਤੇ ਰਾਸ਼ਨ ਸਥਿਰ ਰਹੇਗਾ।</t>
+        </is>
+      </c>
+      <c r="AA177" s="2" t="inlineStr">
+        <is>
+          <t>বহুত তিতা উপাদানে খাদ্যৰ আদৰ্শতকৈ বেছি অংশ লৈছে। ইয়াৰ কিছু অংশ শুকান বিকল্পৰে সলনি কৰিলে শুকান পদাৰ্থ গ্ৰহণ ভাল হ'ব আৰু ৰেচন স্থিৰ থাকিব।</t>
+        </is>
+      </c>
+      <c r="AB177" s="2" t="inlineStr">
+        <is>
+          <t>आहार म्ह घणे गीले घटक आदर्श तै घणे सैं। इनके किमे हिस्से की जगहां सूखा विकल्प देण तै शुष्क पदार्थ सेवन बढ़िया होगा अर आहार स्थिर रहवैगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Tree and shrub forages are important for a balanced diet. Consider increasing their proportion to improve nutritional quality.</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>संतुलित आहार के लिए पेड़ और झाड़ी का चारा महत्वपूर्ण है। पोषण गुणवत्ता सुधारने के लिए इनका अनुपात बढ़ाने पर विचार करें।</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Mahalaga ang forage mula sa puno at palumpong para sa balanseng rasyon. Maaaring dagdagan ang proporsyon nito upang mapabuti ang kalidad ng nutrisyon.</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Hijauan dari pohon dan semak penting untuk ransum yang seimbang. Pertimbangkan untuk menambah proporsinya guna meningkatkan kualitas gizi.</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>อาหารหยาบจากไม้ยืนต้นและไม้พุ่มมีความสำคัญต่อสูตรอาหารที่สมดุล ควรพิจารณาเพิ่มสัดส่วนเพื่อปรับปรุงคุณภาพทางโภชนาการ</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Thức ăn thô từ cây gỗ và cây bụi rất quan trọng cho một khẩu phần cân đối. Bạn nên cân nhắc tăng tỷ lệ của chúng để cải thiện chất lượng dinh dưỡng.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>গাছ ও গুল্ম জাতীয় খাদ্য সুষম খাদ্যের জন্য গুরুত্বপূর্ণ। পুষ্টিমান বাড়াতে এদের অনুপাত বাড়ানোর কথা ভাবুন।</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>सन्तुलित आहारका लागि डाले घाँस र झाडी महत्त्वपूर्ण छन्। पोषणको गुणस्तर सुधार गर्न यिनको अनुपात बढाउने विचार गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>የዛፍ እና የቁጥቋጦ መኖዎች ለተመጣጠነ ራሽን አስፈላጊ ናቸው። የመኖውን ንጥረ-ምግብ ጥራት ለማሻሻል ድርሻቸውን መጨመር ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Baalli mukaa fi daggalaa nyaata madaalawaaf barbaachisoo dha. Qulqullina nyaataa fooyyessuuf qooda isaanii dabaluu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>መግቢ ኦምን ቆጥቋጥን ንሚዛናዊ መግቢ ኣገደስቲ እዮም። ጽሬት ኣመጋግባ ንምምሕያሽ ብጽሒቶም ምውሳኽ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>Les fourrages d'arbres et d'arbustes sont importants pour une ration équilibrée. Pensez à augmenter leur part pour améliorer la valeur nutritive.</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>أعلاف الأشجار والشجيرات مهمة لعليقة متوازنة. يُنصح بزيادة نسبتها لتحسين القيمة الغذائية.</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Ganyen itace da ciyayi suna da muhimmanci ga daidaitaccen abinci. Ku yi la'akari da ƙara yawansu don inganta ingancin abinci.</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>Malisho ya miti na vichaka ni muhimu kwa lishe yenye mizani. Fikiria kuongeza sehemu yake ili kuboresha ubora wa lishe.</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>Mahuti ma mĩtĩ na tũthaka nĩ ma bata harĩ irio iiganĩire. Ciria kũongerera gĩcunjĩ kĩao nĩguo wagĩrie ũgima wa irio.</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>ಸಮತೋಲಿತ ಆಹಾರಕ್ಕೆ ಮರ ಮತ್ತು ಪೊದೆ ಮೇವು ಮುಖ್ಯ. ಪೋಷಕಾಂಶ ಗುಣಮಟ್ಟ ಸುಧಾರಿಸಲು ಅವುಗಳ ಪ್ರಮಾಣವನ್ನು ಹೆಚ್ಚಿಸುವುದನ್ನು ಪರಿಗಣಿಸಿ.</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>சமச்சீர் தீவனத்திற்கு மரம் மற்றும் புதர் தீவனங்கள் முக்கியம். ஊட்டச்சத்துத் தரத்தை மேம்படுத்த அவற்றின் விகிதத்தை அதிகரிப்பதைக் கருதுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>സന്തുലിത തീറ്റയ്ക്ക് മരങ്ങളിൽ നിന്നും കുറ്റിച്ചെടികളിൽ നിന്നുമുള്ള തീറ്റ പ്രധാനമാണ്. പോഷകഗുണം മെച്ചപ്പെടുത്താൻ അവയുടെ അനുപാതം കൂട്ടുന്നത് പരിഗണിക്കുക.</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>संतुलित आहारासाठी झाडपाला आणि झुडपांचा चारा महत्त्वाचा आहे. पोषणाचा दर्जा सुधारण्यासाठी त्यांचे प्रमाण वाढवण्याचा विचार करा.</t>
+        </is>
+      </c>
+      <c r="V178" s="2" t="inlineStr">
+        <is>
+          <t>సమతుల్య ఆహారానికి చెట్లు, పొదల మేత ముఖ్యం. పోషక నాణ్యతను మెరుగుపరచడానికి వాటి నిష్పత్తిని పెంచడం పరిశీలించండి.</t>
+        </is>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>ઝાડ અને ઝાડીનો ચારો સંતુલિત આહાર માટે મહત્વનો છે. પોષણ ગુણવત્તા સુધારવા માટે તેનું પ્રમાણ વધારવાનું વિચારો.</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>संतुलित आहार खातर पेड़ अर झाड़ी रो चारो (जियां खेजड़ी री लूंग) जरूरी है। पोषण री गुणवत्ता सुधारण खातर इणां रो अनुपात बधावण री सोचो।</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>ଗଛ ଓ ବୁଦା ଚାରା ସନ୍ତୁଳିତ ଖାଦ୍ୟ ପାଇଁ ଗୁରୁତ୍ୱପୂର୍ଣ୍ଣ। ପୁଷ୍ଟିମାନ ଉନ୍ନତ କରିବା ପାଇଁ ଏହାର ଅନୁପାତ ବଢ଼ାଇବା କଥା ବିଚାର କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z178" s="2" t="inlineStr">
+        <is>
+          <t>ਰੁੱਖ ਅਤੇ ਝਾੜੀ ਚਾਰਾ ਸੰਤੁਲਿਤ ਖੁਰਾਕ ਲਈ ਮਹੱਤਵਪੂਰਨ ਹੈ। ਪੋਸ਼ਣ ਗੁਣਵੱਤਾ ਸੁਧਾਰਨ ਲਈ ਇਸ ਦਾ ਹਿੱਸਾ ਵਧਾਉਣ ਬਾਰੇ ਸੋਚੋ।</t>
+        </is>
+      </c>
+      <c r="AA178" s="2" t="inlineStr">
+        <is>
+          <t>গছ আৰু জোপোহা জাতীয় খাদ্য সুষম খাদ্যৰ বাবে গুৰুত্বপূৰ্ণ। পুষ্টিমান উন্নত কৰিবলৈ ইয়াৰ অনুপাত বঢ়োৱাৰ কথা বিবেচনা কৰক।</t>
+        </is>
+      </c>
+      <c r="AB178" s="2" t="inlineStr">
+        <is>
+          <t>संतुलित आहार खातर पेड़ अर झाड़ी का चारा जरूरी सै। पोषण की गुणवत्ता सुधारण खातर इनका अनुपात बधाण की सोचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>To reach a more optimal balance, try adding more diverse feed options such as high-quality green fodder or energy supplements.</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>बेहतर संतुलन तक पहुँचने के लिए अच्छी गुणवत्ता का हरा चारा या ऊर्जा पूरक जैसे और विविध आहार विकल्प जोड़कर देखें।</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Para makamit ang mas mainam na balanse, subukang magdagdag ng mas iba't ibang pakain tulad ng de-kalidad na sariwang damo o energy supplement.</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Untuk mencapai keseimbangan yang lebih optimal, cobalah menambah pilihan pakan yang lebih beragam seperti hijauan segar berkualitas tinggi atau suplemen energi.</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>เพื่อให้ได้สมดุลที่เหมาะสมยิ่งขึ้น ลองเพิ่มอาหารที่หลากหลายมากขึ้น เช่น หญ้าสดคุณภาพดี หรืออาหารเสริมพลังงาน</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Để đạt sự cân bằng tốt hơn, hãy thử bổ sung thêm nhiều loại thức ăn đa dạng như cỏ xanh chất lượng cao hoặc thức ăn bổ sung năng lượng.</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>আরও উপযুক্ত ভারসাম্যে পৌঁছাতে আরও বৈচিত্র্যময় খাদ্য যোগ করে দেখুন, যেমন উন্নতমানের সবুজ ঘাস বা শক্তির সম্পূরক খাদ্য।</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>अझ राम्रो सन्तुलनमा पुग्न राम्रो गुणस्तरको हरियो घाँस वा ऊर्जा पूरक जस्ता थप विविध दाना-घाँसका विकल्प थपेर हेर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>የተሻለ ሚዛን ለማግኘት፣ እንደ ጥራት ያለው አረንጓዴ መኖ ወይም የኃይል ተጨማሪዎች ያሉ የተለያዩ መኖዎችን ለመጨመር ይሞክሩ።</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>Madaallii caalaa ga'uuf, nyaata gosa garaa garaa kan akka marga magariisaa qulqullina olaanaa qabu ykn dabalata humnaa dabaluu yaalaa.</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>ዝሓሸ ሚዛን ንምብጻሕ፣ ከም ጽሬት ዘለዎ ቀጠልያ ሳዕሪ ወይ ተወሰኽቲ ጸዓት ዝኣመሰሉ ዝተፈላለዩ መግብታት ምውሳኽ ፈትኑ።</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>Pour atteindre un meilleur équilibre, essayez d'ajouter des aliments plus variés, comme du fourrage vert de bonne qualité ou des compléments énergétiques.</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>لبلوغ توازن أفضل، حاول إضافة خيارات أعلاف أكثر تنوعًا مثل العلف الأخضر عالي الجودة أو مكمّلات الطاقة.</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Don samun daidaito mafi kyau, ku gwada ƙara nau'o'in abinci daban-daban kamar ɗanyar ciyawa mai inganci ko ƙarin abinci na kuzari.</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>Ili kufikia mizani bora zaidi, jaribu kuongeza aina mbalimbali za vyakula kama malisho mabichi bora au virutubisho vya nishati.</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>Nĩguo ũkinye mũiganĩro mwega makĩria, geria kũongerera mĩthemba mĩingĩ ya irio ta nyeki njega ĩrĩ nduru kana irio cia kũongerera hinya.</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>ಹೆಚ್ಚು ಸೂಕ್ತ ಸಮತೋಲನ ತಲುಪಲು, ಉತ್ತಮ ಗುಣಮಟ್ಟದ ಹಸಿರು ಮೇವು ಅಥವಾ ಶಕ್ತಿ ಪೂರಕಗಳಂತಹ ವೈವಿಧ್ಯಮಯ ಆಹಾರ ಆಯ್ಕೆಗಳನ್ನು ಸೇರಿಸಿ ನೋಡಿ.</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>மேலும் உகந்த சமநிலையை அடைய, உயர்தரப் பசுந்தீவனம் அல்லது ஆற்றல் துணைத் தீவனங்கள் போன்ற பல்வேறு தீவன வகைகளைச் சேர்த்துப் பாருங்கள்.</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>കൂടുതൽ അനുയോജ്യമായ സന്തുലനത്തിലെത്താൻ, നല്ലയിനം പച്ചപ്പുല്ല് അല്ലെങ്കിൽ ഊർജ്ജ അനുബന്ധങ്ങൾ പോലുള്ള വൈവിധ്യമാർന്ന തീറ്റകൾ ചേർത്തു നോക്കുക.</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>अधिक चांगले संतुलन साधण्यासाठी चांगल्या प्रतीचा हिरवा चारा किंवा ऊर्जा पूरक यांसारखे अधिक वैविध्यपूर्ण खाद्य पर्याय घालून पाहा.</t>
+        </is>
+      </c>
+      <c r="V179" s="2" t="inlineStr">
+        <is>
+          <t>మరింత సరైన సమతుల్యత కోసం, మంచి నాణ్యమైన పచ్చి మేత లేదా శక్తి అనుబంధాలు వంటి విభిన్న మేత రకాలను కలిపి చూడండి.</t>
+        </is>
+      </c>
+      <c r="W179" s="2" t="inlineStr">
+        <is>
+          <t>વધુ યોગ્ય સંતુલન મેળવવા માટે વિવિધ પ્રકારનો ખોરાક ઉમેરી જુઓ, જેમ કે સારી ગુણવત્તાનો લીલો ચારો કે ઊર્જા પૂરક.</t>
+        </is>
+      </c>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>बेहतर संतुलन तांई पूगण खातर बढ़िया हरो चारो या ऊर्जा पूरक जिसा अलग-अलग दाणा-चारा मिलाय नै देखो।</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr">
+        <is>
+          <t>ଅଧିକ ଉପଯୁକ୍ତ ସନ୍ତୁଳନରେ ପହଞ୍ଚିବା ପାଇଁ ବିଭିନ୍ନ ପ୍ରକାରର ଖାଦ୍ୟ ମିଶାଇ ଦେଖନ୍ତୁ, ଯେପରିକି ଉନ୍ନତମାନର ସବୁଜ ଚାରା କିମ୍ବା ଶକ୍ତି ପରିପୂରକ।</t>
+        </is>
+      </c>
+      <c r="Z179" s="2" t="inlineStr">
+        <is>
+          <t>ਵਧੇਰੇ ਢੁਕਵਾਂ ਸੰਤੁਲਨ ਹਾਸਲ ਕਰਨ ਲਈ ਵੱਖ-ਵੱਖ ਕਿਸਮ ਦੇ ਖੁਰਾਕੀ ਪਦਾਰਥ ਪਾ ਕੇ ਦੇਖੋ, ਜਿਵੇਂ ਚੰਗੀ ਗੁਣਵੱਤਾ ਵਾਲਾ ਹਰਾ ਚਾਰਾ ਜਾਂ ਊਰਜਾ ਪੂਰਕ।</t>
+        </is>
+      </c>
+      <c r="AA179" s="2" t="inlineStr">
+        <is>
+          <t>অধিক উপযুক্ত ভাৰসাম্যত উপনীত হ'বলৈ বিভিন্ন ধৰণৰ খাদ্য যোগ কৰি চাওক, যেনে উন্নত মানৰ সেউজীয়া ঘাঁহ বা শক্তিৰ পৰিপূৰক খাদ্য।</t>
+        </is>
+      </c>
+      <c r="AB179" s="2" t="inlineStr">
+        <is>
+          <t>बढ़िया संतुलन ताईं पहोंचण खातर बढ़िया हरा चारा या ऊर्जा पूरक जिसे न्यारे-न्यारे दाणे-चारे मिला कै देखो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Consider adding basic forages such as grass or straw to support a more balanced and healthy diet.</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (advice)</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>अधिक संतुलित और स्वस्थ आहार के लिए घास या भूसे जैसा बुनियादी चारा जोड़ने पर विचार करें।</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Maaaring magdagdag ng mga pangunahing forage tulad ng damo o dayami upang suportahan ang mas balanse at malusog na rasyon.</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Pertimbangkan untuk menambahkan hijauan dasar seperti rumput atau jerami untuk mendukung ransum yang lebih seimbang dan sehat.</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>ควรพิจารณาเพิ่มอาหารหยาบพื้นฐาน เช่น หญ้าหรือฟาง เพื่อให้สูตรอาหารสมดุลและดีต่อสุขภาพมากขึ้น</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Bạn nên cân nhắc bổ sung các loại thức ăn thô cơ bản như cỏ hoặc rơm để có khẩu phần cân đối và tốt cho sức khỏe hơn.</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>আরও সুষম ও স্বাস্থ্যকর খাদ্যের জন্য ঘাস বা খড়ের মতো মৌলিক আঁশজাতীয় খাদ্য যোগ করার কথা ভাবুন।</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>अझ सन्तुलित र स्वस्थ आहारका लागि घाँस वा पराल जस्ता आधारभूत घाँस-चारा थप्ने विचार गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>የበለጠ የተመጣጠነ እና ጤናማ ራሽን ለማግኘት፣ እንደ ሳር ወይም ገለባ ያሉ መሠረታዊ ሻካራ መኖዎችን መጨመር ያስቡበት።</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Nyaata caalaa madaalawaa fi fayyaa qabu argachuuf, marga bu'uuraa kan akka margaa ykn citaa dabaluu yaadaa.</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>ዝያዳ ሚዛናውን ጥዑይን መግቢ ንምርካብ፣ ከም ሳዕሪ ወይ ሓሰር ዝኣመሰሉ መሰረታዊ መግብታት ምውሳኽ ሕሰቡሉ።</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>Pensez à ajouter des fourrages de base comme de l'herbe ou de la paille pour une ration plus équilibrée et plus saine.</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>يُنصح بإضافة أعلاف خشنة أساسية مثل الحشائش أو التبن لدعم عليقة أكثر توازنًا وصحة.</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Ku yi la'akari da ƙara ciyawa ta asali kamar ciyawa ko karmami don samun abinci mafi daidaito da lafiya.</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>Fikiria kuongeza malisho ya msingi kama nyasi au majani makavu ili kusaidia lishe yenye mizani na afya zaidi.</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>Ciria kũongerera irio cia mũthingi ta nyeki kana mahuti momũ nĩguo irio iiganĩre na irĩ na ũgima makĩria.</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>ಹೆಚ್ಚು ಸಮತೋಲಿತ ಮತ್ತು ಆರೋಗ್ಯಕರ ಆಹಾರಕ್ಕಾಗಿ ಹುಲ್ಲು ಅಥವಾ ಒಣಹುಲ್ಲಿನಂತಹ ಮೂಲ ಮೇವುಗಳನ್ನು ಸೇರಿಸುವುದನ್ನು ಪರಿಗಣಿಸಿ.</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>மேலும் சமச்சீரான, ஆரோக்கியமான தீவனத்திற்கு புல் அல்லது வைக்கோல் போன்ற அடிப்படை முரட்டுத் தீவனங்களைச் சேர்ப்பதைக் கருதுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>കൂടുതൽ സന്തുലിതവും ആരോഗ്യകരവുമായ തീറ്റയ്ക്കായി പുല്ല് അല്ലെങ്കിൽ വൈക്കോൽ പോലുള്ള അടിസ്ഥാന പരുഷാഹാരങ്ങൾ ചേർക്കുന്നത് പരിഗണിക്കുക.</t>
+        </is>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>अधिक संतुलित आणि निरोगी आहारासाठी गवत किंवा काड यांसारखा मूलभूत चारा घालण्याचा विचार करा.</t>
+        </is>
+      </c>
+      <c r="V180" s="2" t="inlineStr">
+        <is>
+          <t>మరింత సమతుల్యమైన, ఆరోగ్యకరమైన ఆహారం కోసం గడ్డి లేదా వరిగడ్డి వంటి ప్రాథమిక గ్రాసాలను కలపడం పరిశీలించండి.</t>
+        </is>
+      </c>
+      <c r="W180" s="2" t="inlineStr">
+        <is>
+          <t>વધુ સંતુલિત અને તંદુરસ્ત આહાર માટે ઘાસ કે પરાળ જેવો મૂળભૂત ઘાસચારો ઉમેરવાનું વિચારો.</t>
+        </is>
+      </c>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>बेसी संतुलित अर स्वस्थ आहार खातर घास या भूसो जिसो मूल चारो मिलावण री सोचो।</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr">
+        <is>
+          <t>ଅଧିକ ସନ୍ତୁଳିତ ଓ ସୁସ୍ଥ ଖାଦ୍ୟ ପାଇଁ ଘାସ କିମ୍ବା ପାଳ ଭଳି ମୌଳିକ ଚାରା ମିଶାଇବା କଥା ବିଚାର କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z180" s="2" t="inlineStr">
+        <is>
+          <t>ਵਧੇਰੇ ਸੰਤੁਲਿਤ ਅਤੇ ਸਿਹਤਮੰਦ ਖੁਰਾਕ ਲਈ ਘਾਹ ਜਾਂ ਤੂੜੀ ਵਰਗੇ ਬੁਨਿਆਦੀ ਚਾਰੇ ਪਾਉਣ ਬਾਰੇ ਸੋਚੋ।</t>
+        </is>
+      </c>
+      <c r="AA180" s="2" t="inlineStr">
+        <is>
+          <t>অধিক সুষম আৰু স্বাস্থ্যকৰ খাদ্যৰ বাবে ঘাঁহ বা খেৰৰ দৰে মূল আঁহযুক্ত খাদ্য যোগ কৰাৰ কথা বিবেচনা কৰক।</t>
+        </is>
+      </c>
+      <c r="AB180" s="2" t="inlineStr">
+        <is>
+          <t>और संतुलित अर ठीक आहार खातर घास या तूड़ा जिसा मूल चारा मिलाण की सोचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Continue monitoring animal performance and adjust as needed.</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>App screen - recommendation (diet meets all targets)</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>पशु के उत्पादन और स्वास्थ्य पर नज़र रखते रहें और ज़रूरत के अनुसार बदलाव करें।</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Patuloy na bantayan ang performance ng hayop at mag-adjust kung kinakailangan.</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Terus pantau performa ternak dan sesuaikan bila perlu.</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>ติดตามสมรรถภาพของสัตว์อย่างต่อเนื่อง และปรับสูตรอาหารตามความจำเป็น</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Tiếp tục theo dõi năng suất của vật nuôi và điều chỉnh khi cần.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>পশুর উৎপাদন ও অবস্থা নিয়মিত পর্যবেক্ষণ করুন এবং প্রয়োজনমতো পরিবর্তন করুন।</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>पशुको उत्पादन र स्वास्थ्यको निगरानी गरिरहनुहोस् र आवश्यकताअनुसार मिलाउनुहोस्।</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>የእንስሳውን አፈጻጸም መከታተልዎን ይቀጥሉ፣ እንደ አስፈላጊነቱም ያስተካክሉ።</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Raawwii horii hordofuu itti fufaa, akka barbaachisummaa isaattis sirreessaa.</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>ኣፈጻጽማ እንስሳ ምክትታል ቀጽሉ፣ ከም ኣድላይነቱ ድማ ኣመዓራርዩ።</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>Continuez à suivre les performances de l'animal et ajustez si nécessaire.</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>استمر في متابعة أداء الحيوان وعدّل العليقة حسب الحاجة.</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Ku ci gaba da lura da yadda dabbar ke yi kuma ku gyara yadda ake buƙata.</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>Endelea kufuatilia utendaji wa mnyama na urekebishe inapohitajika.</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>Thiĩ na mbere gũthuthuria ũrĩa nyamũ ĩrathiĩ na ũcenjie kũringana na bata.</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>ಪ್ರಾಣಿಯ ಕಾರ್ಯಕ್ಷಮತೆಯನ್ನು ಗಮನಿಸುತ್ತಿರಿ ಮತ್ತು ಅಗತ್ಯವಿದ್ದಂತೆ ಬದಲಾವಣೆ ಮಾಡಿ.</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>கால்நடையின் செயல்திறனைத் தொடர்ந்து கண்காணித்து, தேவைக்கேற்ப மாற்றங்கள் செய்யுங்கள்.</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr">
+        <is>
+          <t>ഉരുവിന്റെ പ്രകടനം തുടർന്നും നിരീക്ഷിച്ച് ആവശ്യാനുസരണം മാറ്റങ്ങൾ വരുത്തുക.</t>
+        </is>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>जनावराचे उत्पादन आणि आरोग्य यावर लक्ष ठेवत राहा आणि गरजेनुसार बदल करा.</t>
+        </is>
+      </c>
+      <c r="V181" s="2" t="inlineStr">
+        <is>
+          <t>పశువు పనితీరును గమనిస్తూ ఉండండి, అవసరమైనప్పుడు మార్పులు చేయండి.</t>
+        </is>
+      </c>
+      <c r="W181" s="2" t="inlineStr">
+        <is>
+          <t>પશુના ઉત્પાદન અને સ્થિતિ પર નિયમિત નજર રાખો અને જરૂર મુજબ ફેરફાર કરો.</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>पशु रै उत्पादन अर सेहत माथै निजर राखता रैवो अर जरूरत मुजब बदलाव करो।</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr">
+        <is>
+          <t>ପଶୁର ଉତ୍ପାଦନ ଓ ଅବସ୍ଥା ଉପରେ ନିୟମିତ ନଜର ରଖନ୍ତୁ ଏବଂ ଆବଶ୍ୟକ ଅନୁସାରେ ପରିବର୍ତ୍ତନ କରନ୍ତୁ।</t>
+        </is>
+      </c>
+      <c r="Z181" s="2" t="inlineStr">
+        <is>
+          <t>ਪਸ਼ੂ ਦੀ ਪੈਦਾਵਾਰ ਅਤੇ ਹਾਲਤ 'ਤੇ ਲਗਾਤਾਰ ਨਜ਼ਰ ਰੱਖੋ ਅਤੇ ਲੋੜ ਅਨੁਸਾਰ ਬਦਲਾਅ ਕਰੋ।</t>
+        </is>
+      </c>
+      <c r="AA181" s="2" t="inlineStr">
+        <is>
+          <t>পশুৰ উৎপাদন আৰু অৱস্থা নিয়মীয়াকৈ নিৰীক্ষণ কৰি থাকক আৰু প্ৰয়োজন অনুসৰি সলনি কৰক।</t>
+        </is>
+      </c>
+      <c r="AB181" s="2" t="inlineStr">
+        <is>
+          <t>पशु के उत्पादन अर सेहत पै निगाह राखदे रहो अर जरूरत के हिसाब तै बदलाव करो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Feed milk only, split between morning and evening. Solid-feed ration formulation does not apply to a baby calf (milk intake only, up to ~8 weeks of age).</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>App screen - baby calf recommendation</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>केवल दूध पिलाएँ, सुबह और शाम में बाँटकर। छोटे बछड़े के लिए ठोस आहार का राशन नहीं बनाया जाता (केवल दूध, लगभग 8 सप्ताह की आयु तक)।</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Gatas lamang ang ipainom, hatiin sa umaga at hapon. Hindi saklaw ng pagbuo ng rasyon ng solidong pakain ang guya (gatas lamang ang iniinom, hanggang ~8 linggong gulang).</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Berikan susu saja, dibagi pada pagi dan sore hari. Penyusunan ransum pakan padat tidak berlaku untuk pedet (hanya minum susu, hingga umur ~8 minggu).</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>ให้นมเพียงอย่างเดียว โดยแบ่งให้ช่วงเช้าและช่วงเย็น การคำนวณสูตรอาหารแข็งไม่ใช้กับลูกโคเล็ก (กินนมเท่านั้น จนถึงอายุประมาณ 8 สัปดาห์)</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ cho uống sữa, chia làm hai cữ sáng và chiều. Việc lập khẩu phần thức ăn đặc không áp dụng cho bê con (chỉ uống sữa, đến khoảng 8 tuần tuổi).</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>শুধু দুধ খাওয়ান, সকাল ও সন্ধ্যায় ভাগ করে। বাছুরের জন্য শক্ত খাদ্যের রেশন তৈরি প্রযোজ্য নয় (শুধু দুধ খাওয়ানো, প্রায় 8 সপ্তাহ বয়স পর্যন্ত)।</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>दूध मात्र खुवाउनुहोस्, बिहान र बेलुका बाँडेर। सानो बाच्छाका लागि ठोस आहार तयार गरिँदैन (दूध मात्र, करिब 8 हप्ताको उमेरसम्म)।</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>ወተት ብቻ ይስጡ፣ በጠዋት እና በማታ ከፍለው። የጠንካራ መኖ ራሽን ቀመር ለወተት ጥጃ አይሠራም (ወተት ብቻ፣ እስከ ~8 ሳምንት ዕድሜ ድረስ)።</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Aannan qofa kennaa, ganamaa fi galgala qoodaa. Qophiin nyaata jabaa jabbii xiqqaaf hin hojjetu (aannan qofa, hanga umurii torban ~8tti).</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>ጸባ ጥራይ ሃቡ፣ ንግሆን ምሸትን ተማቒሉ። ቀመር ጽኑዕ መግቢ ንንእሽቶ ምራኽ ኣይምልከትን እዩ (ጸባ ጥራይ፣ ክሳብ ~8 ሰሙን ዕድመ)።</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>Donnez uniquement du lait, réparti entre le matin et le soir. Le calcul d'une ration d'aliments solides ne s'applique pas à un veau non sevré (lait uniquement, jusqu'à ~8 semaines d'âge).</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>قدّم الحليب فقط، مقسّمًا بين الصباح والمساء. لا تنطبق تركيبة عليقة الأعلاف الصلبة على العجل الرضيع (حليب فقط، حتى عمر ~8 أسابيع).</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Ku ba da madara kawai, ku raba ta tsakanin safe da yamma. Tsara abinci mai tauri bai shafi ƙaramin maraƙi ba (madara kawai, har zuwa makonni ~8 da haihuwa).</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>Lisha maziwa pekee, yakigawanywa asubuhi na jioni. Upangaji wa lishe ya chakula kigumu hauhusu ndama mchanga (maziwa pekee, hadi umri wa wiki ~8).</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>Hea iria tu, rĩgayanĩtio rũciinĩ na hwaĩ-inĩ. Gũthondeka irio nyũmũ gũtirĩ kwa bata harĩ njaũ nini (iria tu, nginya ĩkinye wiki ~8).</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>ಹಾಲನ್ನು ಮಾತ್ರ ಕುಡಿಸಿ, ಬೆಳಿಗ್ಗೆ ಮತ್ತು ಸಂಜೆ ಎಂದು ಹಂಚಿ ನೀಡಿ. ಎಳೆ ಕರುವಿಗೆ ಘನ ಆಹಾರದ ಪಡಿತರ ರೂಪಿಸುವುದು ಅನ್ವಯಿಸುವುದಿಲ್ಲ (ಹಾಲು ಮಾತ್ರ, ~8 ವಾರಗಳ ವಯಸ್ಸಿನವರೆಗೆ).</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>பால் மட்டும் புகட்டுங்கள்; காலை, மாலை என இரண்டு வேளையாகப் பிரித்துக் கொடுங்கள். இளம் கன்றுக்குத் திடத் தீவனக் கணக்கீடு பொருந்தாது (பால் மட்டும், ~8 வார வயது வரை).</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr">
+        <is>
+          <t>പാൽ മാത്രം നൽകുക, രാവിലെയും വൈകുന്നേരവുമായി വീതിച്ച്. കിടാവിന് ഖരാഹാര തീറ്റ തയ്യാറാക്കൽ ബാധകമല്ല (പാൽ മാത്രം, ~8 ആഴ്ച പ്രായം വരെ).</t>
+        </is>
+      </c>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>फक्त दूध पाजा, सकाळ आणि संध्याकाळ असे विभागून. लहान वासरासाठी घन खाद्याचा आहार तयार केला जात नाही (फक्त दूध, सुमारे 8 आठवडे वयापर्यंत).</t>
+        </is>
+      </c>
+      <c r="V182" s="2" t="inlineStr">
+        <is>
+          <t>పాలు మాత్రమే తాగించండి, ఉదయం మరియు సాయంత్రం రెండు పూటలుగా పంచి ఇవ్వండి. లేగ దూడకు ఘన ఆహార రేషన్ రూపొందించడం వర్తించదు (పాలు మాత్రమే, ~8 వారాల వయస్సు వరకు).</t>
+        </is>
+      </c>
+      <c r="W182" s="2" t="inlineStr">
+        <is>
+          <t>ફક્ત દૂધ પીવડાવો, સવાર અને સાંજ વચ્ચે વહેંચીને. નાના વાછરડા માટે ઘન આહારનું રાશન બનાવવાનું લાગુ પડતું નથી (ફક્ત દૂધ, આશરે 8 અઠવાડિયાની ઉંમર સુધી).</t>
+        </is>
+      </c>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>फगत दूध पावो, सुबह अर सांझ में बांट नै। छोटा टोगड़ा खातर ठोस आहार कोनी बणायो जावै (फगत दूध, लगभग 8 हफ्ता री उमर तांई)।</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr">
+        <is>
+          <t>କେବଳ କ୍ଷୀର ଖୁଆନ୍ତୁ, ସକାଳ ଓ ସନ୍ଧ୍ୟାରେ ଭାଗ କରି। ଛୋଟ ବାଛୁରୀ ପାଇଁ କଠିନ ଖାଦ୍ୟ ରାସନ ପ୍ରସ୍ତୁତି ପ୍ରଯୁଜ୍ୟ ନୁହେଁ (କେବଳ କ୍ଷୀର, ପ୍ରାୟ 8 ସପ୍ତାହ ବୟସ ପର୍ଯ୍ୟନ୍ତ)।</t>
+        </is>
+      </c>
+      <c r="Z182" s="2" t="inlineStr">
+        <is>
+          <t>ਸਿਰਫ਼ ਦੁੱਧ ਪਿਲਾਓ, ਸਵੇਰੇ ਅਤੇ ਸ਼ਾਮ ਨੂੰ ਵੰਡ ਕੇ। ਛੋਟੇ ਵੱਛੇ ਲਈ ਠੋਸ ਖੁਰਾਕ ਦਾ ਰਾਸ਼ਨ ਬਣਾਉਣਾ ਲਾਗੂ ਨਹੀਂ ਹੁੰਦਾ (ਸਿਰਫ਼ ਦੁੱਧ, ਲਗਭਗ 8 ਹਫ਼ਤਿਆਂ ਦੀ ਉਮਰ ਤੱਕ)।</t>
+        </is>
+      </c>
+      <c r="AA182" s="2" t="inlineStr">
+        <is>
+          <t>কেৱল গাখীৰ খুৱাওক, পুৱা আৰু গধূলি ভাগ কৰি। সৰু দামুৰিৰ বাবে টান খাদ্যৰ ৰেচন প্ৰস্তুত কৰাটো প্ৰযোজ্য নহয় (কেৱল গাখীৰ, প্ৰায় 8 সপ্তাহ বয়সলৈকে)।</t>
+        </is>
+      </c>
+      <c r="AB182" s="2" t="inlineStr">
+        <is>
+          <t>सिर्फ दूध प्याओ, सुबह अर सांझ नै बांट कै। छोटे बाछड़े खातर ठोस आहार कोनी बणाया जांदा (सिर्फ दूध, लगभग 8 हफ्ते की उमर ताईं)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: entered maximum {entered} kg DM/day was reduced to {limit} kg DM/day by the mineral safety limit.</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>App screen - limit warning; keep every {...} exactly ({feed} = feed name, others = numbers)</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: दर्ज अधिकतम {entered} kg DM/day को खनिज सुरक्षा सीमा के कारण घटाकर {limit} kg DM/day किया गया।</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ang inilagay na maximum na {entered} kg DM/day ay ibinaba sa {limit} kg DM/day dahil sa safety limit para sa mineral.</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: batas maksimum yang dimasukkan {entered} kg DM/day dikurangi menjadi {limit} kg DM/day oleh batas keamanan mineral.</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ค่าสูงสุดที่ป้อนไว้ {entered} kg DM/day ถูกลดลงเหลือ {limit} kg DM/day ตามขีดจำกัดความปลอดภัยของแร่ธาตุ</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: mức tối đa đã nhập {entered} kg DM/day đã được giảm xuống {limit} kg DM/day theo giới hạn an toàn khoáng chất.</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: দেওয়া সর্বোচ্চ {entered} kg DM/day খনিজের নিরাপত্তা সীমার কারণে কমিয়ে {limit} kg DM/day করা হয়েছে।</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: प्रविष्ट गरिएको अधिकतम {entered} kg DM/day खनिज सुरक्षा सीमाका कारण घटाएर {limit} kg DM/day गरियो।</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: የገባው ከፍተኛ መጠን {entered} kg DM/day በማዕድን የደህንነት ገደብ ምክንያት ወደ {limit} kg DM/day ዝቅ ተደርጓል።</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: hammi guddaan galfame {entered} kg DM/day daangaa nageenya albuudaatiin gara {limit} kg DM/day tti hir'ifameera.</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ዝኣተወ ዝለዓለ መጠን {entered} kg DM/day ብደረት ድሕነት ማዕድን ናብ {limit} kg DM/day ተቐኒሱ።</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>{feed} : le maximum saisi de {entered} kg DM/day a été réduit à {limit} kg DM/day par la limite de sécurité minérale.</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: تم تخفيض الحد الأقصى المُدخل {entered} kg DM/day إلى {limit} kg DM/day بسبب حد الأمان للمعادن.</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: mafi yawan da aka shigar {entered} kg DM/day an rage shi zuwa {limit} kg DM/day saboda iyakar tsaro ta ma'adinai.</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: kiwango cha juu kilichowekwa cha {entered} kg DM/day kilipunguzwa hadi {limit} kg DM/day kwa kikomo cha usalama wa madini.</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: kĩrĩa kĩnene mũno kĩandĩkĩtwo {entered} kg DM/day nĩ kĩnyihĩtio nginya {limit} kg DM/day nĩ ũndũ wa mũhaka wa ũgitĩri wa mineral.</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ನಮೂದಿಸಿದ ಗರಿಷ್ಠ {entered} kg DM/day ಅನ್ನು ಖನಿಜ ಸುರಕ್ಷತಾ ಮಿತಿಯಿಂದಾಗಿ {limit} kg DM/day ಗೆ ಇಳಿಸಲಾಗಿದೆ.</t>
+        </is>
+      </c>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: உள்ளிட்ட அதிகபட்சம் {entered} kg DM/day, தாது உப்புப் பாதுகாப்பு வரம்பின் காரணமாக {limit} kg DM/day ஆகக் குறைக்கப்பட்டது.</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: നൽകിയ പരമാവധി {entered} kg DM/day, ധാതു സുരക്ഷാ പരിധി കാരണം {limit} kg DM/day ആയി കുറച്ചു.</t>
+        </is>
+      </c>
+      <c r="U183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: नोंदवलेली कमाल {entered} kg DM/day मर्यादा खनिज सुरक्षा मर्यादेमुळे {limit} kg DM/day पर्यंत कमी केली.</t>
+        </is>
+      </c>
+      <c r="V183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: నమోదు చేసిన గరిష్ఠం {entered} kg DM/day, ఖనిజ భద్రతా పరిమితి కారణంగా {limit} kg DM/day కి తగ్గించబడింది.</t>
+        </is>
+      </c>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: દાખલ કરેલી મહત્તમ {entered} kg DM/day ખનીજ સલામતી મર્યાદાને કારણે ઘટાડીને {limit} kg DM/day કરવામાં આવી.</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: भरी गई अधिकतम {entered} kg DM/day खनिज सुरक्षा सीमा रै कारण घटाय नै {limit} kg DM/day करी गई।</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ଦିଆଯାଇଥିବା ସର୍ବାଧିକ {entered} kg DM/day ଖଣିଜ ସୁରକ୍ଷା ସୀମା କାରଣରୁ କମାଇ {limit} kg DM/day କରାଗଲା।</t>
+        </is>
+      </c>
+      <c r="Z183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ਦਰਜ ਕੀਤੀ ਵੱਧ ਤੋਂ ਵੱਧ ਮਾਤਰਾ {entered} kg DM/day ਨੂੰ ਖਣਿਜ ਸੁਰੱਖਿਆ ਹੱਦ ਕਾਰਨ ਘਟਾ ਕੇ {limit} kg DM/day ਕੀਤਾ ਗਿਆ।</t>
+        </is>
+      </c>
+      <c r="AA183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: দিয়া সৰ্বাধিক {entered} kg DM/day খনিজৰ সুৰক্ষা সীমাৰ বাবে কমাই {limit} kg DM/day কৰা হৈছে।</t>
+        </is>
+      </c>
+      <c r="AB183" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: भरी होई अधिकतम {entered} kg DM/day खनिज सुरक्षा सीमा के कारण घटा कै {limit} kg DM/day करी गई।</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: the required mineral minimum of {minimum} kg DM/day could not be met because the entered maximum limits it to {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>App screen - limit warning; keep every {...} exactly ({feed} = feed name, others = numbers)</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: आवश्यक न्यूनतम खनिज {minimum} kg DM/day पूरा नहीं हो सका, क्योंकि दर्ज अधिकतम सीमा इसे {entered} kg DM/day तक ही रखती है।</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: hindi naabot ang kinakailangang minimum na mineral na {minimum} kg DM/day dahil nililimitahan ito ng inilagay na maximum sa {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: kebutuhan minimum mineral sebesar {minimum} kg DM/day tidak dapat dipenuhi karena batas maksimum yang dimasukkan membatasinya pada {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ไม่สามารถให้ได้ถึงปริมาณแร่ธาตุขั้นต่ำที่กำหนด {minimum} kg DM/day เนื่องจากค่าสูงสุดที่ป้อนไว้จำกัดไว้ที่ {entered} kg DM/day</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: không thể đáp ứng mức khoáng tối thiểu bắt buộc {minimum} kg DM/day vì mức tối đa đã nhập chỉ cho phép {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: খনিজের প্রয়োজনীয় ন্যূনতম {minimum} kg DM/day পূরণ করা যায়নি, কারণ দেওয়া সর্বোচ্চ সীমা এটিকে {entered} kg DM/day-এ সীমিত রাখে।</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: आवश्यक न्यूनतम खनिज {minimum} kg DM/day पूरा हुन सकेन, किनभने प्रविष्ट गरिएको अधिकतमले यसलाई {entered} kg DM/day मा सीमित गर्छ।</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: የሚያስፈልገው ዝቅተኛ የማዕድን መጠን {minimum} kg DM/day ሊሟላ አልቻለም፤ ምክንያቱም የገባው ከፍተኛ መጠን ወደ {entered} kg DM/day ይገድበዋል።</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: hammi albuudaa xiqqaan barbaachisu {minimum} kg DM/day guutamuu hin dandeenye, sababni isaas hammi guddaan galfame gara {entered} kg DM/day tti daangeessa.</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ዘድሊ ዝተሓተ መጠን ማዕድን {minimum} kg DM/day ክማላእ ኣይከኣለን፣ ምኽንያቱ ዝኣተወ ዝለዓለ መጠን ናብ {entered} kg DM/day ይድርቶ።</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>{feed} : le minimum minéral requis de {minimum} kg DM/day n'a pas pu être atteint, car le maximum saisi le limite à {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: تعذّر تحقيق الحد الأدنى المطلوب من المعادن وهو {minimum} kg DM/day لأن الحد الأقصى المُدخل يقيّده عند {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ba a iya cimma mafi ƙarancin ma'adinai da ake buƙata na {minimum} kg DM/day ba saboda mafi yawan da aka shigar ya iyakance shi zuwa {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: kiwango cha chini cha madini kinachohitajika cha {minimum} kg DM/day hakikuweza kufikiwa kwa sababu kiwango cha juu kilichowekwa kinakibana hadi {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: mineral nini mũno ĩrĩa ĩbataranĩtie {minimum} kg DM/day ndĩngĩakinyirwo tondũ kĩrĩa kĩnene mũno kĩandĩkĩtwo nĩ kĩmĩhingĩte nginya {entered} kg DM/day.</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ನಮೂದಿಸಿದ ಗರಿಷ್ಠ ಮಿತಿ ಇದನ್ನು {entered} kg DM/day ಗೆ ಸೀಮಿತಗೊಳಿಸುವುದರಿಂದ, ಅಗತ್ಯವಿರುವ ಕನಿಷ್ಠ ಖನಿಜ ಪ್ರಮಾಣ {minimum} kg DM/day ಪೂರೈಸಲು ಸಾಧ್ಯವಾಗಲಿಲ್ಲ.</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: உள்ளிட்ட அதிகபட்ச வரம்பு இதை {entered} kg DM/day ஆகக் கட்டுப்படுத்துவதால், தேவையான குறைந்தபட்ச தாது அளவு {minimum} kg DM/day பூர்த்தி செய்ய முடியவில்லை.</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: നൽകിയ പരമാവധി പരിധി ഇതിനെ {entered} kg DM/day ആയി പരിമിതപ്പെടുത്തുന്നതിനാൽ, ആവശ്യമായ കുറഞ്ഞ ധാതു അളവായ {minimum} kg DM/day പാലിക്കാനായില്ല.</t>
+        </is>
+      </c>
+      <c r="U184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: आवश्यक किमान खनिज {minimum} kg DM/day पूर्ण होऊ शकले नाही, कारण नोंदवलेली कमाल मर्यादा ते {entered} kg DM/day पर्यंतच ठेवते.</t>
+        </is>
+      </c>
+      <c r="V184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: నమోదు చేసిన గరిష్ఠ పరిమితి దీన్ని {entered} kg DM/day కి పరిమితం చేస్తున్నందున, అవసరమైన కనీస ఖనిజ పరిమాణం {minimum} kg DM/day అందించలేకపోయాం.</t>
+        </is>
+      </c>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: જરૂરી લઘુત્તમ ખનીજ પ્રમાણ {minimum} kg DM/day પૂરું થઈ શક્યું નથી, કારણ કે દાખલ કરેલી મહત્તમ મર્યાદા તેને {entered} kg DM/day સુધી સીમિત કરે છે.</t>
+        </is>
+      </c>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: जरूरी न्यूनतम खनिज {minimum} kg DM/day पूरो कोनी हो सक्यो, क्यूंकि भरी गई अधिकतम सीमा इणनै {entered} kg DM/day तांई रोकै।</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ଆବଶ୍ୟକ ସର୍ବନିମ୍ନ ଖଣିଜ ମାତ୍ରା {minimum} kg DM/day ପୂରଣ କରାଯାଇପାରିଲା ନାହିଁ, କାରଣ ଦିଆଯାଇଥିବା ସର୍ବାଧିକ ସୀମା ଏହାକୁ {entered} kg DM/day ରେ ସୀମିତ କରେ।</t>
+        </is>
+      </c>
+      <c r="Z184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ਖਣਿਜ ਦੀ ਲੋੜੀਂਦੀ ਘੱਟੋ-ਘੱਟ ਮਾਤਰਾ {minimum} kg DM/day ਪੂਰੀ ਨਹੀਂ ਹੋ ਸਕੀ, ਕਿਉਂਕਿ ਦਰਜ ਕੀਤੀ ਵੱਧ ਤੋਂ ਵੱਧ ਹੱਦ ਇਸ ਨੂੰ {entered} kg DM/day ਤੱਕ ਸੀਮਤ ਕਰਦੀ ਹੈ।</t>
+        </is>
+      </c>
+      <c r="AA184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: খনিজৰ প্ৰয়োজনীয় ন্যূনতম {minimum} kg DM/day পূৰণ কৰিব পৰা নগ'ল, কাৰণ দিয়া সৰ্বাধিক সীমাই ইয়াক {entered} kg DM/day লৈ সীমিত কৰে।</t>
+        </is>
+      </c>
+      <c r="AB184" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: जरूरी न्यूनतम खनिज {minimum} kg DM/day पूरा कोनी हो सक्या, क्यूंके भरी होई अधिकतम सीमा इसनै {entered} kg DM/day ताईं रोकै सै।</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: entered maximum {entered} kg DM/day was reduced to {limit} kg DM/day by the urea safety limit (shared across {count} urea feed(s)).</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>App screen - limit warning; keep every {...} exactly ({feed} = feed name, others = numbers)</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: दर्ज अधिकतम {entered} kg DM/day को यूरिया सुरक्षा सीमा के कारण घटाकर {limit} kg DM/day किया गया ({count} यूरिया वाली आहार सामग्रियों में साझा)।</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ang inilagay na maximum na {entered} kg DM/day ay ibinaba sa {limit} kg DM/day dahil sa safety limit para sa urea (pinaghahatian ng {count} na pakaing may urea).</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: batas maksimum yang dimasukkan {entered} kg DM/day dikurangi menjadi {limit} kg DM/day oleh batas keamanan urea (dibagi untuk {count} pakan yang mengandung urea).</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ค่าสูงสุดที่ป้อนไว้ {entered} kg DM/day ถูกลดลงเหลือ {limit} kg DM/day ตามขีดจำกัดความปลอดภัยของยูเรีย (ใช้ร่วมกันระหว่างอาหารที่มียูเรีย {count} รายการ)</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: mức tối đa đã nhập {entered} kg DM/day đã được giảm xuống {limit} kg DM/day theo giới hạn an toàn urê (dùng chung cho {count} loại thức ăn chứa urê).</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: দেওয়া সর্বোচ্চ {entered} kg DM/day ইউরিয়ার নিরাপত্তা সীমার কারণে কমিয়ে {limit} kg DM/day করা হয়েছে ({count}টি ইউরিয়াযুক্ত খাদ্যের মধ্যে ভাগ করা)।</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: प्रविष्ट गरिएको अधिकतम {entered} kg DM/day युरिया सुरक्षा सीमाका कारण घटाएर {limit} kg DM/day गरियो ({count} वटा युरियायुक्त दानामा बाँडिएको)।</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: የገባው ከፍተኛ መጠን {entered} kg DM/day በዩሪያ የደህንነት ገደብ ምክንያት ወደ {limit} kg DM/day ዝቅ ተደርጓል (ገደቡ ዩሪያ ባላቸው {count} መኖዎች መካከል የተጋራ ነው)።</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: hammi guddaan galfame {entered} kg DM/day daangaa nageenya yuuriyaatiin gara {limit} kg DM/day tti hir'ifameera (daangaan kun nyaata yuuriyaa qaban {count} gidduutti qoodameera).</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ዝኣተወ ዝለዓለ መጠን {entered} kg DM/day ብደረት ድሕነት ዩሪያ ናብ {limit} kg DM/day ተቐኒሱ (እቲ ደረት ኣብ መንጎ {count} ዩሪያ ዘለዎም መግብታት ዝተኻፈለ እዩ)።</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>{feed} : le maximum saisi de {entered} kg DM/day a été réduit à {limit} kg DM/day par la limite de sécurité de l'urée (partagée entre {count} aliment(s) à base d'urée).</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: تم تخفيض الحد الأقصى المُدخل {entered} kg DM/day إلى {limit} kg DM/day بسبب حد الأمان لليوريا (مشترك بين {count} من أعلاف اليوريا).</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: mafi yawan da aka shigar {entered} kg DM/day an rage shi zuwa {limit} kg DM/day saboda iyakar tsaro ta yuriya (iyakar ana raba ta tsakanin abinci {count} masu yuriya).</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: kiwango cha juu kilichowekwa cha {entered} kg DM/day kilipunguzwa hadi {limit} kg DM/day kwa kikomo cha usalama wa urea (kikomo hiki kinashirikiwa na vyakula {count} vyenye urea).</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: kĩrĩa kĩnene mũno kĩandĩkĩtwo {entered} kg DM/day nĩ kĩnyihĩtio nginya {limit} kg DM/day nĩ ũndũ wa mũhaka wa ũgitĩri wa urea (mũhaka ũcio nĩ ũgayanĩtwo nĩ irio {count} irĩ na urea).</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ನಮೂದಿಸಿದ ಗರಿಷ್ಠ {entered} kg DM/day ಅನ್ನು ಯೂರಿಯಾ ಸುರಕ್ಷತಾ ಮಿತಿಯಿಂದಾಗಿ {limit} kg DM/day ಗೆ ಇಳಿಸಲಾಗಿದೆ ({count} ಯೂರಿಯಾ ಆಹಾರಗಳ ನಡುವೆ ಹಂಚಲಾಗಿದೆ).</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: உள்ளிட்ட அதிகபட்சம் {entered} kg DM/day, யூரியா பாதுகாப்பு வரம்பின் காரணமாக {limit} kg DM/day ஆகக் குறைக்கப்பட்டது ({count} யூரியா தீவனங்களுக்கிடையே பகிரப்பட்டது).</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: നൽകിയ പരമാവധി {entered} kg DM/day, യൂറിയ സുരക്ഷാ പരിധി കാരണം {limit} kg DM/day ആയി കുറച്ചു ({count} യൂറിയ തീറ്റകൾക്കിടയിൽ പങ്കിട്ടത്).</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: नोंदवलेली कमाल {entered} kg DM/day मर्यादा युरिया सुरक्षा मर्यादेमुळे {limit} kg DM/day पर्यंत कमी केली ({count} युरियायुक्त खाद्यांमध्ये विभागून).</t>
+        </is>
+      </c>
+      <c r="V185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: నమోదు చేసిన గరిష్ఠం {entered} kg DM/day, యూరియా భద్రతా పరిమితి కారణంగా {limit} kg DM/day కి తగ్గించబడింది ({count} యూరియా మేతల మధ్య పంచుకోబడింది).</t>
+        </is>
+      </c>
+      <c r="W185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: દાખલ કરેલી મહત્તમ {entered} kg DM/day યુરિયા સલામતી મર્યાદાને કારણે ઘટાડીને {limit} kg DM/day કરવામાં આવી ({count} યુરિયાવાળા ખોરાક વચ્ચે વહેંચાયેલી મર્યાદા).</t>
+        </is>
+      </c>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: भरी गई अधिकतम {entered} kg DM/day यूरिया सुरक्षा सीमा रै कारण घटाय नै {limit} kg DM/day करी गई ({count} यूरिया वाला दाणा में बंटी थकी)।</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ଦିଆଯାଇଥିବା ସର୍ବାଧିକ {entered} kg DM/day ୟୁରିଆ ସୁରକ୍ଷା ସୀମା କାରଣରୁ କମାଇ {limit} kg DM/day କରାଗଲା ({count}ଟି ୟୁରିଆଯୁକ୍ତ ଖାଦ୍ୟ ମଧ୍ୟରେ ଭାଗ କରାଯାଇଛି)।</t>
+        </is>
+      </c>
+      <c r="Z185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: ਦਰਜ ਕੀਤੀ ਵੱਧ ਤੋਂ ਵੱਧ ਮਾਤਰਾ {entered} kg DM/day ਨੂੰ ਯੂਰੀਆ ਸੁਰੱਖਿਆ ਹੱਦ ਕਾਰਨ ਘਟਾ ਕੇ {limit} kg DM/day ਕੀਤਾ ਗਿਆ ({count} ਯੂਰੀਆ ਵਾਲੇ ਖੁਰਾਕੀ ਪਦਾਰਥਾਂ ਵਿੱਚ ਸਾਂਝੀ ਹੱਦ)।</t>
+        </is>
+      </c>
+      <c r="AA185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: দিয়া সৰ্বাধিক {entered} kg DM/day ইউৰিয়াৰ সুৰক্ষা সীমাৰ বাবে কমাই {limit} kg DM/day কৰা হৈছে ({count}টা ইউৰিয়াযুক্ত খাদ্যৰ মাজত ভাগ কৰি)।</t>
+        </is>
+      </c>
+      <c r="AB185" s="2" t="inlineStr">
+        <is>
+          <t>{feed}: भरी होई अधिकतम {entered} kg DM/day यूरिया सुरक्षा सीमा के कारण घटा कै {limit} kg DM/day करी गई ({count} यूरिया आले दाणे म्ह बंटी होई)।</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23642,7 +26766,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -23678,7 +26801,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -23700,7 +26822,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
